--- a/Tests/Validation/Wheat/UoM_WheatProject/Gnarwarre2024_Observed.xlsx
+++ b/Tests/Validation/Wheat/UoM_WheatProject/Gnarwarre2024_Observed.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BL180"/>
+  <dimension ref="A1:BL184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
@@ -873,7 +873,7 @@
         <v>45492</v>
       </c>
       <c r="BL14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1013,16 +1013,10 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>45530</v>
-      </c>
-      <c r="F22">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="Y22">
-        <v>9.033333333333333</v>
-      </c>
-      <c r="AM22">
-        <v>17.83333333333333</v>
+        <v>45529</v>
+      </c>
+      <c r="BL22">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1032,10 +1026,16 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <v>45531</v>
-      </c>
-      <c r="BD23">
-        <v>0.4986534762522178</v>
+        <v>45530</v>
+      </c>
+      <c r="F23">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Y23">
+        <v>9.033333333333333</v>
+      </c>
+      <c r="AM23">
+        <v>17.83333333333333</v>
       </c>
     </row>
     <row r="24">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <v>45539</v>
+        <v>45531</v>
       </c>
       <c r="BD24">
-        <v>0.5757412838706862</v>
+        <v>0.4986534762522178</v>
       </c>
     </row>
     <row r="25">
@@ -1058,25 +1058,10 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <v>45548</v>
-      </c>
-      <c r="F25">
-        <v>0.645</v>
-      </c>
-      <c r="H25">
-        <v>0.4405343891660297</v>
-      </c>
-      <c r="I25">
-        <v>0.3656951882495262</v>
-      </c>
-      <c r="J25">
-        <v>0.23686494554914</v>
-      </c>
-      <c r="K25">
-        <v>0.1223765262972183</v>
-      </c>
-      <c r="Y25">
-        <v>11.525</v>
+        <v>45539</v>
+      </c>
+      <c r="BD25">
+        <v>0.5757412838706862</v>
       </c>
     </row>
     <row r="26">
@@ -1086,10 +1071,25 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <v>45551</v>
-      </c>
-      <c r="AM26">
-        <v>41.58333333333333</v>
+        <v>45548</v>
+      </c>
+      <c r="F26">
+        <v>0.645</v>
+      </c>
+      <c r="H26">
+        <v>0.4405343891660297</v>
+      </c>
+      <c r="I26">
+        <v>0.3656951882495262</v>
+      </c>
+      <c r="J26">
+        <v>0.23686494554914</v>
+      </c>
+      <c r="K26">
+        <v>0.1223765262972183</v>
+      </c>
+      <c r="Y26">
+        <v>11.525</v>
       </c>
     </row>
     <row r="27">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <v>45554</v>
+        <v>45551</v>
       </c>
       <c r="AM27">
-        <v>44.58333333333335</v>
+        <v>41.58333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -1112,16 +1112,10 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <v>45558</v>
-      </c>
-      <c r="F28">
-        <v>0.6475</v>
-      </c>
-      <c r="Y28">
-        <v>12.35</v>
-      </c>
-      <c r="BD28">
-        <v>0.7190365989034946</v>
+        <v>45554</v>
+      </c>
+      <c r="AM28">
+        <v>44.58333333333335</v>
       </c>
     </row>
     <row r="29">
@@ -1133,8 +1127,14 @@
       <c r="B29" s="2">
         <v>45558</v>
       </c>
-      <c r="BL29">
-        <v>6</v>
+      <c r="F29">
+        <v>0.6475</v>
+      </c>
+      <c r="Y29">
+        <v>12.35</v>
+      </c>
+      <c r="BD29">
+        <v>0.7190365989034946</v>
       </c>
     </row>
     <row r="30">
@@ -1144,70 +1144,10 @@
         </is>
       </c>
       <c r="B30" s="2">
-        <v>45561</v>
-      </c>
-      <c r="F30">
-        <v>0.725</v>
-      </c>
-      <c r="G30">
-        <v>720.785606604451</v>
-      </c>
-      <c r="N30">
-        <v>0.9573626680410601</v>
-      </c>
-      <c r="U30">
-        <v>151.8594692019315</v>
-      </c>
-      <c r="Z30">
-        <v>53.1</v>
-      </c>
-      <c r="AA30">
-        <v>58.775</v>
-      </c>
-      <c r="AB30">
-        <v>54.8</v>
-      </c>
-      <c r="AC30">
-        <v>53.5</v>
-      </c>
-      <c r="AI30">
-        <v>77.66165718703395</v>
-      </c>
-      <c r="AJ30">
-        <v>490.307117547444</v>
-      </c>
-      <c r="AL30">
-        <v>567.9687747344783</v>
-      </c>
-      <c r="AM30">
-        <v>66.25</v>
-      </c>
-      <c r="AR30">
-        <v>-24.55</v>
-      </c>
-      <c r="AS30">
-        <v>0.0414935</v>
-      </c>
-      <c r="AT30">
-        <v>8.895</v>
-      </c>
-      <c r="AU30">
-        <v>-24.1875</v>
-      </c>
-      <c r="AV30">
-        <v>0.023545</v>
-      </c>
-      <c r="AW30">
-        <v>22.4575</v>
-      </c>
-      <c r="AX30">
-        <v>-24.9125</v>
-      </c>
-      <c r="BB30">
-        <v>0.01580425</v>
-      </c>
-      <c r="BC30">
-        <v>23.7625</v>
+        <v>45558</v>
+      </c>
+      <c r="BL30">
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1217,10 +1157,70 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <v>45565</v>
-      </c>
-      <c r="W31">
-        <v>267.762499999999</v>
+        <v>45561</v>
+      </c>
+      <c r="F31">
+        <v>0.725</v>
+      </c>
+      <c r="G31">
+        <v>720.785606604451</v>
+      </c>
+      <c r="N31">
+        <v>0.9573626680410601</v>
+      </c>
+      <c r="U31">
+        <v>151.8594692019315</v>
+      </c>
+      <c r="Z31">
+        <v>53.1</v>
+      </c>
+      <c r="AA31">
+        <v>58.775</v>
+      </c>
+      <c r="AB31">
+        <v>54.8</v>
+      </c>
+      <c r="AC31">
+        <v>53.5</v>
+      </c>
+      <c r="AI31">
+        <v>77.66165718703395</v>
+      </c>
+      <c r="AJ31">
+        <v>490.307117547444</v>
+      </c>
+      <c r="AL31">
+        <v>567.9687747344783</v>
+      </c>
+      <c r="AM31">
+        <v>66.25</v>
+      </c>
+      <c r="AR31">
+        <v>-24.55</v>
+      </c>
+      <c r="AS31">
+        <v>0.0414935</v>
+      </c>
+      <c r="AT31">
+        <v>8.895</v>
+      </c>
+      <c r="AU31">
+        <v>-24.1875</v>
+      </c>
+      <c r="AV31">
+        <v>0.023545</v>
+      </c>
+      <c r="AW31">
+        <v>22.4575</v>
+      </c>
+      <c r="AX31">
+        <v>-24.9125</v>
+      </c>
+      <c r="BB31">
+        <v>0.01580425</v>
+      </c>
+      <c r="BC31">
+        <v>23.7625</v>
       </c>
     </row>
     <row r="32">
@@ -1230,25 +1230,10 @@
         </is>
       </c>
       <c r="B32" s="2">
-        <v>45566</v>
-      </c>
-      <c r="F32">
-        <v>0.5975</v>
-      </c>
-      <c r="O32">
-        <v>3.75</v>
-      </c>
-      <c r="P32">
-        <v>12.55833333333332</v>
-      </c>
-      <c r="Q32">
-        <v>1.441666666666668</v>
-      </c>
-      <c r="R32">
-        <v>15.33333333333333</v>
-      </c>
-      <c r="S32">
-        <v>14.91666666666667</v>
+        <v>45565</v>
+      </c>
+      <c r="W32">
+        <v>267.762499999999</v>
       </c>
     </row>
     <row r="33">
@@ -1258,10 +1243,25 @@
         </is>
       </c>
       <c r="B33" s="2">
-        <v>45568</v>
-      </c>
-      <c r="BD33">
-        <v>0.678214723553506</v>
+        <v>45566</v>
+      </c>
+      <c r="F33">
+        <v>0.5975</v>
+      </c>
+      <c r="O33">
+        <v>3.75</v>
+      </c>
+      <c r="P33">
+        <v>12.55833333333332</v>
+      </c>
+      <c r="Q33">
+        <v>1.441666666666668</v>
+      </c>
+      <c r="R33">
+        <v>15.33333333333333</v>
+      </c>
+      <c r="S33">
+        <v>14.91666666666667</v>
       </c>
     </row>
     <row r="34">
@@ -1271,25 +1271,10 @@
         </is>
       </c>
       <c r="B34" s="2">
-        <v>45569</v>
-      </c>
-      <c r="F34">
-        <v>0.6225000000000001</v>
-      </c>
-      <c r="H34">
-        <v>0.47451498229747</v>
-      </c>
-      <c r="I34">
-        <v>0.35079282774175</v>
-      </c>
-      <c r="J34">
-        <v>0.306157026790804</v>
-      </c>
-      <c r="K34">
-        <v>0.2114371989345499</v>
-      </c>
-      <c r="AM34">
-        <v>70</v>
+        <v>45568</v>
+      </c>
+      <c r="BD34">
+        <v>0.678214723553506</v>
       </c>
     </row>
     <row r="35">
@@ -1301,8 +1286,23 @@
       <c r="B35" s="2">
         <v>45569</v>
       </c>
-      <c r="BL35">
-        <v>7</v>
+      <c r="F35">
+        <v>0.6225000000000001</v>
+      </c>
+      <c r="H35">
+        <v>0.47451498229747</v>
+      </c>
+      <c r="I35">
+        <v>0.35079282774175</v>
+      </c>
+      <c r="J35">
+        <v>0.306157026790804</v>
+      </c>
+      <c r="K35">
+        <v>0.2114371989345499</v>
+      </c>
+      <c r="AM35">
+        <v>70</v>
       </c>
     </row>
     <row r="36">
@@ -1312,91 +1312,10 @@
         </is>
       </c>
       <c r="B36" s="2">
-        <v>45581</v>
-      </c>
-      <c r="F36">
-        <v>0.5175000000000001</v>
-      </c>
-      <c r="G36">
-        <v>856.0944680468108</v>
-      </c>
-      <c r="H36">
-        <v>0.5895698295575575</v>
-      </c>
-      <c r="I36">
-        <v>0.390074380024396</v>
-      </c>
-      <c r="J36">
-        <v>0.247006373799732</v>
-      </c>
-      <c r="K36">
-        <v>0.1319367824245427</v>
-      </c>
-      <c r="N36">
-        <v>13.58727289089932</v>
-      </c>
-      <c r="U36">
-        <v>101.6770069793953</v>
-      </c>
-      <c r="AA36">
-        <v>54.65</v>
-      </c>
-      <c r="AB36">
-        <v>54.875</v>
-      </c>
-      <c r="AC36">
-        <v>52.375</v>
-      </c>
-      <c r="AH36">
-        <v>351.6405908628845</v>
-      </c>
-      <c r="AI36">
-        <v>185.5636991643518</v>
-      </c>
-      <c r="AJ36">
-        <v>555.2664890121645</v>
-      </c>
-      <c r="AL36">
-        <v>740.8301881765162</v>
-      </c>
-      <c r="AM36">
-        <v>77.5</v>
-      </c>
-      <c r="AO36">
-        <v>-24.715</v>
-      </c>
-      <c r="AP36">
-        <v>0.01467525</v>
-      </c>
-      <c r="AQ36">
-        <v>4.3125</v>
-      </c>
-      <c r="AR36">
-        <v>-24.485</v>
-      </c>
-      <c r="AS36">
-        <v>0.03710125</v>
-      </c>
-      <c r="AT36">
-        <v>11.18</v>
-      </c>
-      <c r="AU36">
-        <v>-24.485</v>
-      </c>
-      <c r="AV36">
-        <v>0.0215515</v>
-      </c>
-      <c r="AW36">
-        <v>21.86</v>
-      </c>
-      <c r="AX36">
-        <v>-24.845</v>
-      </c>
-      <c r="BB36">
-        <v>0.01380225</v>
-      </c>
-      <c r="BC36">
-        <v>26.845</v>
+        <v>45569</v>
+      </c>
+      <c r="BL36">
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1408,8 +1327,89 @@
       <c r="B37" s="2">
         <v>45581</v>
       </c>
-      <c r="BL37">
-        <v>8</v>
+      <c r="F37">
+        <v>0.5175000000000001</v>
+      </c>
+      <c r="G37">
+        <v>856.0944680468108</v>
+      </c>
+      <c r="H37">
+        <v>0.5895698295575575</v>
+      </c>
+      <c r="I37">
+        <v>0.390074380024396</v>
+      </c>
+      <c r="J37">
+        <v>0.247006373799732</v>
+      </c>
+      <c r="K37">
+        <v>0.1319367824245427</v>
+      </c>
+      <c r="N37">
+        <v>13.58727289089932</v>
+      </c>
+      <c r="U37">
+        <v>101.6770069793953</v>
+      </c>
+      <c r="AA37">
+        <v>54.65</v>
+      </c>
+      <c r="AB37">
+        <v>54.875</v>
+      </c>
+      <c r="AC37">
+        <v>52.375</v>
+      </c>
+      <c r="AH37">
+        <v>351.6405908628845</v>
+      </c>
+      <c r="AI37">
+        <v>185.5636991643518</v>
+      </c>
+      <c r="AJ37">
+        <v>555.2664890121645</v>
+      </c>
+      <c r="AL37">
+        <v>740.8301881765162</v>
+      </c>
+      <c r="AM37">
+        <v>77.5</v>
+      </c>
+      <c r="AO37">
+        <v>-24.715</v>
+      </c>
+      <c r="AP37">
+        <v>0.01467525</v>
+      </c>
+      <c r="AQ37">
+        <v>4.3125</v>
+      </c>
+      <c r="AR37">
+        <v>-24.485</v>
+      </c>
+      <c r="AS37">
+        <v>0.03710125</v>
+      </c>
+      <c r="AT37">
+        <v>11.18</v>
+      </c>
+      <c r="AU37">
+        <v>-24.485</v>
+      </c>
+      <c r="AV37">
+        <v>0.0215515</v>
+      </c>
+      <c r="AW37">
+        <v>21.86</v>
+      </c>
+      <c r="AX37">
+        <v>-24.845</v>
+      </c>
+      <c r="BB37">
+        <v>0.01380225</v>
+      </c>
+      <c r="BC37">
+        <v>26.845</v>
       </c>
     </row>
     <row r="38">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="B38" s="2">
-        <v>45587</v>
-      </c>
-      <c r="X38">
-        <v>290.0943135811557</v>
+        <v>45581</v>
+      </c>
+      <c r="BL38">
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="B39" s="2">
-        <v>45590</v>
-      </c>
-      <c r="BD39">
-        <v>0.4721789075847307</v>
+        <v>45587</v>
+      </c>
+      <c r="X39">
+        <v>290.0943135811557</v>
       </c>
     </row>
     <row r="40">
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="B40" s="2">
-        <v>45597</v>
-      </c>
-      <c r="F40">
-        <v>0.4375</v>
+        <v>45590</v>
+      </c>
+      <c r="BD40">
+        <v>0.4721789075847307</v>
       </c>
     </row>
     <row r="41">
@@ -1458,73 +1458,10 @@
         </is>
       </c>
       <c r="B41" s="2">
-        <v>45603</v>
+        <v>45597</v>
       </c>
       <c r="F41">
-        <v>0.34125</v>
-      </c>
-      <c r="G41">
-        <v>999.7235484405076</v>
-      </c>
-      <c r="N41">
-        <v>51.47017452455748</v>
-      </c>
-      <c r="U41">
-        <v>41.00964293554313</v>
-      </c>
-      <c r="AD41">
-        <v>138.7428745161575</v>
-      </c>
-      <c r="AE41">
-        <v>9941.344216003703</v>
-      </c>
-      <c r="AF41">
-        <v>0.02554225094741685</v>
-      </c>
-      <c r="AG41">
-        <v>253.168400694887</v>
-      </c>
-      <c r="AH41">
-        <v>391.9112752110448</v>
-      </c>
-      <c r="AI41">
-        <v>391.9112752110448</v>
-      </c>
-      <c r="AJ41">
-        <v>479.4767200675245</v>
-      </c>
-      <c r="AK41">
-        <v>618.2195945836822</v>
-      </c>
-      <c r="AO41">
-        <v>-24.2575</v>
-      </c>
-      <c r="AP41">
-        <v>0.0127445</v>
-      </c>
-      <c r="AQ41">
-        <v>6.265</v>
-      </c>
-      <c r="AR41">
-        <v>-24.6925</v>
-      </c>
-      <c r="AS41">
-        <v>0.020635</v>
-      </c>
-      <c r="AT41">
-        <v>15.7825</v>
-      </c>
-      <c r="AX41">
-        <v>-26.0325</v>
-      </c>
-      <c r="BB41">
-        <v>0.00205272</v>
-      </c>
-      <c r="BC41">
-        <v>20.4325</v>
-      </c>
-      <c r="BD41">
-        <v>0.1099172424232266</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="42">
@@ -1534,13 +1471,73 @@
         </is>
       </c>
       <c r="B42" s="2">
-        <v>45604</v>
+        <v>45603</v>
       </c>
       <c r="F42">
-        <v>0.3185714285714286</v>
+        <v>0.34125</v>
+      </c>
+      <c r="G42">
+        <v>999.7235484405076</v>
+      </c>
+      <c r="N42">
+        <v>51.47017452455748</v>
+      </c>
+      <c r="U42">
+        <v>41.00964293554313</v>
+      </c>
+      <c r="AD42">
+        <v>138.7428745161575</v>
+      </c>
+      <c r="AE42">
+        <v>9941.344216003703</v>
+      </c>
+      <c r="AF42">
+        <v>0.02554225094741685</v>
+      </c>
+      <c r="AG42">
+        <v>253.168400694887</v>
+      </c>
+      <c r="AH42">
+        <v>391.9112752110448</v>
+      </c>
+      <c r="AI42">
+        <v>391.9112752110448</v>
+      </c>
+      <c r="AJ42">
+        <v>479.4767200675245</v>
+      </c>
+      <c r="AK42">
+        <v>618.2195945836822</v>
+      </c>
+      <c r="AO42">
+        <v>-24.2575</v>
+      </c>
+      <c r="AP42">
+        <v>0.0127445</v>
+      </c>
+      <c r="AQ42">
+        <v>6.265</v>
+      </c>
+      <c r="AR42">
+        <v>-24.6925</v>
+      </c>
+      <c r="AS42">
+        <v>0.020635</v>
+      </c>
+      <c r="AT42">
+        <v>15.7825</v>
+      </c>
+      <c r="AX42">
+        <v>-26.0325</v>
+      </c>
+      <c r="BB42">
+        <v>0.00205272</v>
+      </c>
+      <c r="BC42">
+        <v>20.4325</v>
       </c>
       <c r="BD42">
-        <v>0.1230256489091058</v>
+        <v>0.1099172424232266</v>
       </c>
     </row>
     <row r="43">
@@ -1550,10 +1547,13 @@
         </is>
       </c>
       <c r="B43" s="2">
-        <v>45608</v>
+        <v>45604</v>
       </c>
       <c r="F43">
-        <v>0.2625</v>
+        <v>0.3185714285714286</v>
+      </c>
+      <c r="BD43">
+        <v>0.1230256489091058</v>
       </c>
     </row>
     <row r="44">
@@ -1565,8 +1565,8 @@
       <c r="B44" s="2">
         <v>45608</v>
       </c>
-      <c r="BL44">
-        <v>10</v>
+      <c r="F44">
+        <v>0.2625</v>
       </c>
     </row>
     <row r="45">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="B45" s="2">
-        <v>45610</v>
-      </c>
-      <c r="BD45">
-        <v>0.03110168825342849</v>
+        <v>45608</v>
+      </c>
+      <c r="BL45">
+        <v>10</v>
       </c>
     </row>
     <row r="46">
@@ -1589,13 +1589,10 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <v>45618</v>
+        <v>45610</v>
       </c>
       <c r="BD46">
-        <v>4.466696187248225e-05</v>
-      </c>
-      <c r="BE46">
-        <v>317.8434003799995</v>
+        <v>0.03110168825342849</v>
       </c>
     </row>
     <row r="47">
@@ -1605,10 +1602,13 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <v>45628</v>
+        <v>45618</v>
       </c>
       <c r="BD47">
-        <v>0</v>
+        <v>4.466696187248225e-05</v>
+      </c>
+      <c r="BE47">
+        <v>317.8434003799995</v>
       </c>
     </row>
     <row r="48">
@@ -1618,78 +1618,10 @@
         </is>
       </c>
       <c r="B48" s="2">
-        <v>45631</v>
-      </c>
-      <c r="G48">
-        <v>882.4076973710403</v>
-      </c>
-      <c r="L48">
-        <v>8415.323381696122</v>
-      </c>
-      <c r="M48">
-        <v>388.5942882016155</v>
-      </c>
-      <c r="N48">
-        <v>90.37778546721857</v>
-      </c>
-      <c r="AD48">
-        <v>91.4963759873676</v>
-      </c>
-      <c r="AE48">
-        <v>9944.529150414255</v>
-      </c>
-      <c r="AF48">
-        <v>0.04616501057619737</v>
-      </c>
-      <c r="AG48">
-        <v>458.6132347351995</v>
-      </c>
-      <c r="AH48">
-        <v>331.9638064637672</v>
-      </c>
-      <c r="AI48">
-        <v>550.109610722567</v>
-      </c>
-      <c r="AJ48">
-        <v>241.9203011812545</v>
-      </c>
-      <c r="AK48">
-        <v>333.4166771686217</v>
-      </c>
-      <c r="AN48">
-        <v>510.8526953526563</v>
-      </c>
-      <c r="AO48">
-        <v>-25.48</v>
-      </c>
-      <c r="AP48">
-        <v>0.01115975</v>
-      </c>
-      <c r="AQ48">
-        <v>6.1075</v>
-      </c>
-      <c r="AX48">
-        <v>-26.04</v>
-      </c>
-      <c r="AY48">
-        <v>-25.62</v>
-      </c>
-      <c r="AZ48">
-        <v>0.008374224999999999</v>
-      </c>
-      <c r="BA48">
-        <v>5.965</v>
-      </c>
-      <c r="BB48">
-        <v>-0.0018107125</v>
-      </c>
-      <c r="BC48">
-        <v>8.102499999999999</v>
-      </c>
-      <c r="BK48" t="inlineStr">
-        <is>
-          <t>HarvestRipe</t>
-        </is>
+        <v>45628</v>
+      </c>
+      <c r="BD48">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1699,35 +1631,103 @@
         </is>
       </c>
       <c r="B49" s="2">
-        <v>45644</v>
-      </c>
-      <c r="BF49">
-        <v>77.875</v>
-      </c>
-      <c r="BG49">
-        <v>11.6625</v>
-      </c>
-      <c r="BH49">
-        <v>10.7875</v>
-      </c>
-      <c r="BI49">
-        <v>1.4875</v>
-      </c>
-      <c r="BJ49">
-        <v>4.239612485638755</v>
+        <v>45631</v>
+      </c>
+      <c r="G49">
+        <v>882.4076973710403</v>
+      </c>
+      <c r="L49">
+        <v>8415.323381696122</v>
+      </c>
+      <c r="M49">
+        <v>388.5942882016155</v>
+      </c>
+      <c r="N49">
+        <v>90.37778546721857</v>
+      </c>
+      <c r="AD49">
+        <v>91.4963759873676</v>
+      </c>
+      <c r="AE49">
+        <v>9944.529150414255</v>
+      </c>
+      <c r="AF49">
+        <v>0.04616501057619737</v>
+      </c>
+      <c r="AG49">
+        <v>458.6132347351995</v>
+      </c>
+      <c r="AH49">
+        <v>331.9638064637672</v>
+      </c>
+      <c r="AI49">
+        <v>550.109610722567</v>
+      </c>
+      <c r="AJ49">
+        <v>241.9203011812545</v>
+      </c>
+      <c r="AK49">
+        <v>333.4166771686217</v>
+      </c>
+      <c r="AN49">
+        <v>510.8526953526563</v>
+      </c>
+      <c r="AO49">
+        <v>-25.48</v>
+      </c>
+      <c r="AP49">
+        <v>0.01115975</v>
+      </c>
+      <c r="AQ49">
+        <v>6.1075</v>
+      </c>
+      <c r="AX49">
+        <v>-26.04</v>
+      </c>
+      <c r="AY49">
+        <v>-25.62</v>
+      </c>
+      <c r="AZ49">
+        <v>0.008374224999999999</v>
+      </c>
+      <c r="BA49">
+        <v>5.965</v>
+      </c>
+      <c r="BB49">
+        <v>-0.0018107125</v>
+      </c>
+      <c r="BC49">
+        <v>8.102499999999999</v>
+      </c>
+      <c r="BK49" t="inlineStr">
+        <is>
+          <t>HarvestRipe</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FAR VIC W24-50CvIllabo</t>
+          <t>FAR VIC W24-50CvBigRed</t>
         </is>
       </c>
       <c r="B50" s="2">
-        <v>45427</v>
-      </c>
-      <c r="BL50">
-        <v>3</v>
+        <v>45644</v>
+      </c>
+      <c r="BF50">
+        <v>77.875</v>
+      </c>
+      <c r="BG50">
+        <v>11.6625</v>
+      </c>
+      <c r="BH50">
+        <v>10.7875</v>
+      </c>
+      <c r="BI50">
+        <v>1.4875</v>
+      </c>
+      <c r="BJ50">
+        <v>4.239612485638755</v>
       </c>
     </row>
     <row r="51">
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="B51" s="2">
-        <v>45434</v>
-      </c>
-      <c r="BD51">
-        <v>0.07520201645597127</v>
+        <v>45427</v>
+      </c>
+      <c r="BL51">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="B52" s="2">
-        <v>45441</v>
-      </c>
-      <c r="Y52">
-        <v>2.741666666666665</v>
+        <v>45434</v>
+      </c>
+      <c r="BD52">
+        <v>0.07520201645597127</v>
       </c>
     </row>
     <row r="53">
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="B53" s="2">
-        <v>45447</v>
+        <v>45441</v>
       </c>
       <c r="Y53">
-        <v>3.15</v>
+        <v>2.741666666666665</v>
       </c>
     </row>
     <row r="54">
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="B54" s="2">
-        <v>45460</v>
+        <v>45447</v>
       </c>
       <c r="Y54">
-        <v>4.083333333333332</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="55">
@@ -1789,13 +1789,10 @@
         </is>
       </c>
       <c r="B55" s="2">
-        <v>45461</v>
-      </c>
-      <c r="E55">
-        <v>0.8693722943722945</v>
-      </c>
-      <c r="F55">
-        <v>0.1725</v>
+        <v>45460</v>
+      </c>
+      <c r="Y55">
+        <v>4.083333333333332</v>
       </c>
     </row>
     <row r="56">
@@ -1805,19 +1802,13 @@
         </is>
       </c>
       <c r="B56" s="2">
-        <v>45467</v>
-      </c>
-      <c r="D56">
-        <v>152.7777777777777</v>
-      </c>
-      <c r="T56">
-        <v>13.67916666666665</v>
-      </c>
-      <c r="V56">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="Y56">
-        <v>4.366666666666667</v>
+        <v>45461</v>
+      </c>
+      <c r="E56">
+        <v>0.8693722943722945</v>
+      </c>
+      <c r="F56">
+        <v>0.1725</v>
       </c>
     </row>
     <row r="57">
@@ -1827,10 +1818,19 @@
         </is>
       </c>
       <c r="B57" s="2">
-        <v>45469</v>
-      </c>
-      <c r="BD57">
-        <v>0.1329294557439328</v>
+        <v>45467</v>
+      </c>
+      <c r="D57">
+        <v>152.7777777777777</v>
+      </c>
+      <c r="T57">
+        <v>13.67916666666665</v>
+      </c>
+      <c r="V57">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="Y57">
+        <v>4.366666666666667</v>
       </c>
     </row>
     <row r="58">
@@ -1840,13 +1840,10 @@
         </is>
       </c>
       <c r="B58" s="2">
-        <v>45474</v>
-      </c>
-      <c r="F58">
-        <v>0.29</v>
-      </c>
-      <c r="Y58">
-        <v>4.775</v>
+        <v>45469</v>
+      </c>
+      <c r="BD58">
+        <v>0.1329294557439328</v>
       </c>
     </row>
     <row r="59">
@@ -1856,10 +1853,13 @@
         </is>
       </c>
       <c r="B59" s="2">
-        <v>45477</v>
-      </c>
-      <c r="BD59">
-        <v>0.1897346317610183</v>
+        <v>45474</v>
+      </c>
+      <c r="F59">
+        <v>0.29</v>
+      </c>
+      <c r="Y59">
+        <v>4.775</v>
       </c>
     </row>
     <row r="60">
@@ -1869,19 +1869,10 @@
         </is>
       </c>
       <c r="B60" s="2">
-        <v>45481</v>
-      </c>
-      <c r="C60">
-        <v>136</v>
-      </c>
-      <c r="T60">
-        <v>13.1</v>
-      </c>
-      <c r="V60">
-        <v>0.375</v>
-      </c>
-      <c r="Y60">
-        <v>5.166666666666665</v>
+        <v>45477</v>
+      </c>
+      <c r="BD60">
+        <v>0.1897346317610183</v>
       </c>
     </row>
     <row r="61">
@@ -1891,10 +1882,10 @@
         </is>
       </c>
       <c r="B61" s="2">
-        <v>45483</v>
+        <v>45478</v>
       </c>
       <c r="BL61">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -1904,10 +1895,19 @@
         </is>
       </c>
       <c r="B62" s="2">
-        <v>45490</v>
-      </c>
-      <c r="BD62">
-        <v>0.2445856817132178</v>
+        <v>45481</v>
+      </c>
+      <c r="C62">
+        <v>136</v>
+      </c>
+      <c r="T62">
+        <v>13.1</v>
+      </c>
+      <c r="V62">
+        <v>0.375</v>
+      </c>
+      <c r="Y62">
+        <v>5.166666666666665</v>
       </c>
     </row>
     <row r="63">
@@ -1917,13 +1917,10 @@
         </is>
       </c>
       <c r="B63" s="2">
-        <v>45495</v>
-      </c>
-      <c r="T63">
-        <v>12.2</v>
-      </c>
-      <c r="V63">
-        <v>0.6166666666666667</v>
+        <v>45490</v>
+      </c>
+      <c r="BD63">
+        <v>0.2445856817132178</v>
       </c>
     </row>
     <row r="64">
@@ -1933,25 +1930,13 @@
         </is>
       </c>
       <c r="B64" s="2">
-        <v>45502</v>
-      </c>
-      <c r="F64">
-        <v>0.4075</v>
+        <v>45495</v>
       </c>
       <c r="T64">
-        <v>15.25555555555557</v>
+        <v>12.2</v>
       </c>
       <c r="V64">
-        <v>0.688888888888889</v>
-      </c>
-      <c r="Y64">
-        <v>7.241666666666665</v>
-      </c>
-      <c r="AM64">
-        <v>22.16666666666665</v>
-      </c>
-      <c r="BD64">
-        <v>0.327487352345576</v>
+        <v>0.6166666666666667</v>
       </c>
     </row>
     <row r="65">
@@ -1961,10 +1946,25 @@
         </is>
       </c>
       <c r="B65" s="2">
-        <v>45506</v>
+        <v>45502</v>
+      </c>
+      <c r="F65">
+        <v>0.4075</v>
+      </c>
+      <c r="T65">
+        <v>15.25555555555557</v>
+      </c>
+      <c r="V65">
+        <v>0.688888888888889</v>
+      </c>
+      <c r="Y65">
+        <v>7.241666666666665</v>
+      </c>
+      <c r="AM65">
+        <v>22.16666666666665</v>
       </c>
       <c r="BD65">
-        <v>0.4307421218782285</v>
+        <v>0.327487352345576</v>
       </c>
     </row>
     <row r="66">
@@ -1974,16 +1974,10 @@
         </is>
       </c>
       <c r="B66" s="2">
-        <v>45509</v>
-      </c>
-      <c r="T66">
-        <v>20.1</v>
-      </c>
-      <c r="V66">
-        <v>0.7</v>
-      </c>
-      <c r="Y66">
-        <v>7.7</v>
+        <v>45506</v>
+      </c>
+      <c r="BD66">
+        <v>0.4307421218782285</v>
       </c>
     </row>
     <row r="67">
@@ -1993,25 +1987,16 @@
         </is>
       </c>
       <c r="B67" s="2">
-        <v>45516</v>
-      </c>
-      <c r="F67">
-        <v>0.4225</v>
+        <v>45509</v>
       </c>
       <c r="T67">
-        <v>18.25</v>
+        <v>20.1</v>
       </c>
       <c r="V67">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="Y67">
-        <v>8.233333333333334</v>
-      </c>
-      <c r="AM67">
-        <v>21.58333333333333</v>
-      </c>
-      <c r="BD67">
-        <v>0.5548183594467858</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="68">
@@ -2021,10 +2006,10 @@
         </is>
       </c>
       <c r="B68" s="2">
-        <v>45523</v>
-      </c>
-      <c r="Y68">
-        <v>9.0625</v>
+        <v>45512</v>
+      </c>
+      <c r="BL68">
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -2034,10 +2019,25 @@
         </is>
       </c>
       <c r="B69" s="2">
-        <v>45525</v>
+        <v>45516</v>
+      </c>
+      <c r="F69">
+        <v>0.4225</v>
+      </c>
+      <c r="T69">
+        <v>18.25</v>
+      </c>
+      <c r="V69">
+        <v>0.825</v>
+      </c>
+      <c r="Y69">
+        <v>8.233333333333334</v>
+      </c>
+      <c r="AM69">
+        <v>21.58333333333333</v>
       </c>
       <c r="BD69">
-        <v>0.4789010088469405</v>
+        <v>0.5548183594467858</v>
       </c>
     </row>
     <row r="70">
@@ -2047,16 +2047,10 @@
         </is>
       </c>
       <c r="B70" s="2">
-        <v>45530</v>
-      </c>
-      <c r="F70">
-        <v>0.575</v>
+        <v>45523</v>
       </c>
       <c r="Y70">
-        <v>9.98333333333335</v>
-      </c>
-      <c r="AM70">
-        <v>28.91666666666667</v>
+        <v>9.0625</v>
       </c>
     </row>
     <row r="71">
@@ -2066,10 +2060,10 @@
         </is>
       </c>
       <c r="B71" s="2">
-        <v>45531</v>
+        <v>45525</v>
       </c>
       <c r="BD71">
-        <v>0.5014561188916941</v>
+        <v>0.4789010088469405</v>
       </c>
     </row>
     <row r="72">
@@ -2079,10 +2073,16 @@
         </is>
       </c>
       <c r="B72" s="2">
-        <v>45539</v>
-      </c>
-      <c r="BD72">
-        <v>0.4719700632777712</v>
+        <v>45530</v>
+      </c>
+      <c r="F72">
+        <v>0.575</v>
+      </c>
+      <c r="Y72">
+        <v>9.98333333333335</v>
+      </c>
+      <c r="AM72">
+        <v>28.91666666666667</v>
       </c>
     </row>
     <row r="73">
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="B73" s="2">
-        <v>45540</v>
-      </c>
-      <c r="BL73">
-        <v>6</v>
+        <v>45531</v>
+      </c>
+      <c r="BD73">
+        <v>0.5014561188916941</v>
       </c>
     </row>
     <row r="74">
@@ -2105,25 +2105,10 @@
         </is>
       </c>
       <c r="B74" s="2">
-        <v>45548</v>
-      </c>
-      <c r="F74">
-        <v>0.59</v>
-      </c>
-      <c r="H74">
-        <v>0.4215878612443085</v>
-      </c>
-      <c r="I74">
-        <v>0.4629932030681965</v>
-      </c>
-      <c r="J74">
-        <v>0.2257947302143352</v>
-      </c>
-      <c r="K74">
-        <v>0.1192351104142804</v>
-      </c>
-      <c r="Y74">
-        <v>11.08333333333333</v>
+        <v>45539</v>
+      </c>
+      <c r="BD74">
+        <v>0.4719700632777712</v>
       </c>
     </row>
     <row r="75">
@@ -2133,10 +2118,10 @@
         </is>
       </c>
       <c r="B75" s="2">
-        <v>45551</v>
-      </c>
-      <c r="AM75">
-        <v>48.91666666666665</v>
+        <v>45540</v>
+      </c>
+      <c r="BL75">
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -2146,10 +2131,25 @@
         </is>
       </c>
       <c r="B76" s="2">
-        <v>45553</v>
-      </c>
-      <c r="BL76">
-        <v>7</v>
+        <v>45548</v>
+      </c>
+      <c r="F76">
+        <v>0.59</v>
+      </c>
+      <c r="H76">
+        <v>0.4215878612443085</v>
+      </c>
+      <c r="I76">
+        <v>0.4629932030681965</v>
+      </c>
+      <c r="J76">
+        <v>0.2257947302143352</v>
+      </c>
+      <c r="K76">
+        <v>0.1192351104142804</v>
+      </c>
+      <c r="Y76">
+        <v>11.08333333333333</v>
       </c>
     </row>
     <row r="77">
@@ -2159,79 +2159,10 @@
         </is>
       </c>
       <c r="B77" s="2">
-        <v>45554</v>
-      </c>
-      <c r="F77">
-        <v>0.6575</v>
-      </c>
-      <c r="G77">
-        <v>527.0219376556248</v>
-      </c>
-      <c r="N77">
-        <v>1.683661363177884</v>
-      </c>
-      <c r="U77">
-        <v>117.2336668961815</v>
-      </c>
-      <c r="Z77">
-        <v>51.175</v>
-      </c>
-      <c r="AA77">
-        <v>51.175</v>
-      </c>
-      <c r="AB77">
-        <v>55.2</v>
-      </c>
-      <c r="AC77">
-        <v>52.025</v>
-      </c>
-      <c r="AI77">
-        <v>93.99629260722863</v>
-      </c>
-      <c r="AJ77">
-        <v>314.1083167890367</v>
-      </c>
-      <c r="AL77">
-        <v>408.1046093962652</v>
+        <v>45551</v>
       </c>
       <c r="AM77">
-        <v>51.58333333333333</v>
-      </c>
-      <c r="AO77">
-        <v>-24.575</v>
-      </c>
-      <c r="AP77">
-        <v>0.0155845</v>
-      </c>
-      <c r="AQ77">
-        <v>9.765000000000001</v>
-      </c>
-      <c r="AR77">
-        <v>-24.4375</v>
-      </c>
-      <c r="AS77">
-        <v>0.04039525</v>
-      </c>
-      <c r="AT77">
-        <v>9.487500000000001</v>
-      </c>
-      <c r="AU77">
-        <v>-24.6375</v>
-      </c>
-      <c r="AV77">
-        <v>0.0218315</v>
-      </c>
-      <c r="AW77">
-        <v>17.1</v>
-      </c>
-      <c r="AX77">
-        <v>-24.985</v>
-      </c>
-      <c r="BB77">
-        <v>0.01313475</v>
-      </c>
-      <c r="BC77">
-        <v>26.2625</v>
+        <v>48.91666666666665</v>
       </c>
     </row>
     <row r="78">
@@ -2241,25 +2172,10 @@
         </is>
       </c>
       <c r="B78" s="2">
-        <v>45558</v>
-      </c>
-      <c r="F78">
-        <v>0.5750000000000001</v>
-      </c>
-      <c r="O78">
-        <v>17.16666666666667</v>
-      </c>
-      <c r="R78">
-        <v>27.25</v>
-      </c>
-      <c r="S78">
-        <v>35.00000000000003</v>
-      </c>
-      <c r="Y78">
-        <v>11.08333333333333</v>
-      </c>
-      <c r="BD78">
-        <v>0.5349182448035327</v>
+        <v>45553</v>
+      </c>
+      <c r="BL78">
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -2269,10 +2185,79 @@
         </is>
       </c>
       <c r="B79" s="2">
-        <v>45565</v>
-      </c>
-      <c r="W79">
-        <v>249.767857142857</v>
+        <v>45554</v>
+      </c>
+      <c r="F79">
+        <v>0.6575</v>
+      </c>
+      <c r="G79">
+        <v>527.0219376556248</v>
+      </c>
+      <c r="N79">
+        <v>1.683661363177884</v>
+      </c>
+      <c r="U79">
+        <v>117.2336668961815</v>
+      </c>
+      <c r="Z79">
+        <v>51.175</v>
+      </c>
+      <c r="AA79">
+        <v>51.175</v>
+      </c>
+      <c r="AB79">
+        <v>55.2</v>
+      </c>
+      <c r="AC79">
+        <v>52.025</v>
+      </c>
+      <c r="AI79">
+        <v>93.99629260722863</v>
+      </c>
+      <c r="AJ79">
+        <v>314.1083167890367</v>
+      </c>
+      <c r="AL79">
+        <v>408.1046093962652</v>
+      </c>
+      <c r="AM79">
+        <v>51.58333333333333</v>
+      </c>
+      <c r="AO79">
+        <v>-24.575</v>
+      </c>
+      <c r="AP79">
+        <v>0.0155845</v>
+      </c>
+      <c r="AQ79">
+        <v>9.765000000000001</v>
+      </c>
+      <c r="AR79">
+        <v>-24.4375</v>
+      </c>
+      <c r="AS79">
+        <v>0.04039525</v>
+      </c>
+      <c r="AT79">
+        <v>9.487500000000001</v>
+      </c>
+      <c r="AU79">
+        <v>-24.6375</v>
+      </c>
+      <c r="AV79">
+        <v>0.0218315</v>
+      </c>
+      <c r="AW79">
+        <v>17.1</v>
+      </c>
+      <c r="AX79">
+        <v>-24.985</v>
+      </c>
+      <c r="BB79">
+        <v>0.01313475</v>
+      </c>
+      <c r="BC79">
+        <v>26.2625</v>
       </c>
     </row>
     <row r="80">
@@ -2282,16 +2267,25 @@
         </is>
       </c>
       <c r="B80" s="2">
-        <v>45566</v>
+        <v>45558</v>
       </c>
       <c r="F80">
-        <v>0.56125</v>
-      </c>
-      <c r="P80">
-        <v>14.5</v>
-      </c>
-      <c r="Q80">
-        <v>1.404166666666665</v>
+        <v>0.5750000000000001</v>
+      </c>
+      <c r="O80">
+        <v>17.16666666666667</v>
+      </c>
+      <c r="R80">
+        <v>27.25</v>
+      </c>
+      <c r="S80">
+        <v>35.00000000000003</v>
+      </c>
+      <c r="Y80">
+        <v>11.08333333333333</v>
+      </c>
+      <c r="BD80">
+        <v>0.5349182448035327</v>
       </c>
     </row>
     <row r="81">
@@ -2301,10 +2295,10 @@
         </is>
       </c>
       <c r="B81" s="2">
-        <v>45567</v>
-      </c>
-      <c r="BL81">
-        <v>8</v>
+        <v>45565</v>
+      </c>
+      <c r="W81">
+        <v>249.767857142857</v>
       </c>
     </row>
     <row r="82">
@@ -2314,10 +2308,16 @@
         </is>
       </c>
       <c r="B82" s="2">
-        <v>45568</v>
-      </c>
-      <c r="BD82">
-        <v>0.4860169251450213</v>
+        <v>45566</v>
+      </c>
+      <c r="F82">
+        <v>0.56125</v>
+      </c>
+      <c r="P82">
+        <v>14.5</v>
+      </c>
+      <c r="Q82">
+        <v>1.404166666666665</v>
       </c>
     </row>
     <row r="83">
@@ -2327,91 +2327,10 @@
         </is>
       </c>
       <c r="B83" s="2">
-        <v>45576</v>
-      </c>
-      <c r="F83">
-        <v>0.505</v>
-      </c>
-      <c r="G83">
-        <v>736.0738722045995</v>
-      </c>
-      <c r="H83">
-        <v>0.5096038053718408</v>
-      </c>
-      <c r="I83">
-        <v>0.406496165063529</v>
-      </c>
-      <c r="J83">
-        <v>0.2839230940434525</v>
-      </c>
-      <c r="K83">
-        <v>0.167756122878724</v>
-      </c>
-      <c r="N83">
-        <v>14.00911580966373</v>
-      </c>
-      <c r="U83">
-        <v>93.64622040523909</v>
-      </c>
-      <c r="AA83">
-        <v>53.575</v>
-      </c>
-      <c r="AB83">
-        <v>53.325</v>
-      </c>
-      <c r="AC83">
-        <v>53.275</v>
-      </c>
-      <c r="AH83">
-        <v>262.2277970208597</v>
-      </c>
-      <c r="AI83">
-        <v>182.8962388718597</v>
-      </c>
-      <c r="AJ83">
-        <v>445.5222971178372</v>
-      </c>
-      <c r="AL83">
-        <v>628.4185359896968</v>
-      </c>
-      <c r="AM83">
-        <v>70</v>
-      </c>
-      <c r="AO83">
-        <v>-24.7225</v>
-      </c>
-      <c r="AP83">
-        <v>0.0181815</v>
-      </c>
-      <c r="AQ83">
-        <v>5.575</v>
-      </c>
-      <c r="AR83">
-        <v>-24.565</v>
-      </c>
-      <c r="AS83">
-        <v>0.03423575</v>
-      </c>
-      <c r="AT83">
-        <v>13.235</v>
-      </c>
-      <c r="AU83">
-        <v>-24.5275</v>
-      </c>
-      <c r="AV83">
-        <v>0.02183525</v>
-      </c>
-      <c r="AW83">
-        <v>23.2</v>
-      </c>
-      <c r="AX83">
-        <v>-25.1775</v>
-      </c>
-      <c r="BB83">
-        <v>0.011342225</v>
-      </c>
-      <c r="BC83">
-        <v>23.29</v>
+        <v>45567</v>
+      </c>
+      <c r="BL83">
+        <v>8</v>
       </c>
     </row>
     <row r="84">
@@ -2421,10 +2340,10 @@
         </is>
       </c>
       <c r="B84" s="2">
-        <v>45587</v>
-      </c>
-      <c r="X84">
-        <v>276.7636363636358</v>
+        <v>45568</v>
+      </c>
+      <c r="BD84">
+        <v>0.4860169251450213</v>
       </c>
     </row>
     <row r="85">
@@ -2434,10 +2353,91 @@
         </is>
       </c>
       <c r="B85" s="2">
-        <v>45590</v>
-      </c>
-      <c r="BD85">
-        <v>0.248742385631483</v>
+        <v>45576</v>
+      </c>
+      <c r="F85">
+        <v>0.505</v>
+      </c>
+      <c r="G85">
+        <v>736.0738722045995</v>
+      </c>
+      <c r="H85">
+        <v>0.5096038053718408</v>
+      </c>
+      <c r="I85">
+        <v>0.406496165063529</v>
+      </c>
+      <c r="J85">
+        <v>0.2839230940434525</v>
+      </c>
+      <c r="K85">
+        <v>0.167756122878724</v>
+      </c>
+      <c r="N85">
+        <v>14.00911580966373</v>
+      </c>
+      <c r="U85">
+        <v>93.64622040523909</v>
+      </c>
+      <c r="AA85">
+        <v>53.575</v>
+      </c>
+      <c r="AB85">
+        <v>53.325</v>
+      </c>
+      <c r="AC85">
+        <v>53.275</v>
+      </c>
+      <c r="AH85">
+        <v>262.2277970208597</v>
+      </c>
+      <c r="AI85">
+        <v>182.8962388718597</v>
+      </c>
+      <c r="AJ85">
+        <v>445.5222971178372</v>
+      </c>
+      <c r="AL85">
+        <v>628.4185359896968</v>
+      </c>
+      <c r="AM85">
+        <v>70</v>
+      </c>
+      <c r="AO85">
+        <v>-24.7225</v>
+      </c>
+      <c r="AP85">
+        <v>0.0181815</v>
+      </c>
+      <c r="AQ85">
+        <v>5.575</v>
+      </c>
+      <c r="AR85">
+        <v>-24.565</v>
+      </c>
+      <c r="AS85">
+        <v>0.03423575</v>
+      </c>
+      <c r="AT85">
+        <v>13.235</v>
+      </c>
+      <c r="AU85">
+        <v>-24.5275</v>
+      </c>
+      <c r="AV85">
+        <v>0.02183525</v>
+      </c>
+      <c r="AW85">
+        <v>23.2</v>
+      </c>
+      <c r="AX85">
+        <v>-25.1775</v>
+      </c>
+      <c r="BB85">
+        <v>0.011342225</v>
+      </c>
+      <c r="BC85">
+        <v>23.29</v>
       </c>
     </row>
     <row r="86">
@@ -2447,67 +2447,10 @@
         </is>
       </c>
       <c r="B86" s="2">
-        <v>45595</v>
-      </c>
-      <c r="G86">
-        <v>683.6229212356873</v>
-      </c>
-      <c r="N86">
-        <v>23.20246752623583</v>
-      </c>
-      <c r="U86">
-        <v>38.2235693412399</v>
-      </c>
-      <c r="AD86">
-        <v>99.52198823122762</v>
-      </c>
-      <c r="AE86">
-        <v>6853.281737360559</v>
-      </c>
-      <c r="AF86">
-        <v>0.0225478399734957</v>
-      </c>
-      <c r="AG86">
-        <v>154.209573001553</v>
-      </c>
-      <c r="AH86">
-        <v>253.7315612327805</v>
-      </c>
-      <c r="AI86">
-        <v>253.7315612327805</v>
-      </c>
-      <c r="AJ86">
-        <v>316.51791029734</v>
-      </c>
-      <c r="AK86">
-        <v>416.0398985285677</v>
-      </c>
-      <c r="AO86">
-        <v>-24.245</v>
-      </c>
-      <c r="AP86">
-        <v>0.012783</v>
-      </c>
-      <c r="AQ86">
-        <v>6.3725</v>
-      </c>
-      <c r="AR86">
-        <v>-25.1125</v>
-      </c>
-      <c r="AS86">
-        <v>0.02081925</v>
-      </c>
-      <c r="AT86">
-        <v>16.185</v>
-      </c>
-      <c r="AX86">
-        <v>-26.1325</v>
-      </c>
-      <c r="BB86">
-        <v>0.0014708375</v>
-      </c>
-      <c r="BC86">
-        <v>21.1825</v>
+        <v>45587</v>
+      </c>
+      <c r="X86">
+        <v>276.7636363636358</v>
       </c>
     </row>
     <row r="87">
@@ -2517,10 +2460,10 @@
         </is>
       </c>
       <c r="B87" s="2">
-        <v>45597</v>
-      </c>
-      <c r="F87">
-        <v>0.33125</v>
+        <v>45590</v>
+      </c>
+      <c r="BD87">
+        <v>0.248742385631483</v>
       </c>
     </row>
     <row r="88">
@@ -2530,10 +2473,67 @@
         </is>
       </c>
       <c r="B88" s="2">
-        <v>45600</v>
-      </c>
-      <c r="BL88">
-        <v>10</v>
+        <v>45595</v>
+      </c>
+      <c r="G88">
+        <v>683.6229212356873</v>
+      </c>
+      <c r="N88">
+        <v>23.20246752623583</v>
+      </c>
+      <c r="U88">
+        <v>38.2235693412399</v>
+      </c>
+      <c r="AD88">
+        <v>99.52198823122762</v>
+      </c>
+      <c r="AE88">
+        <v>6853.281737360559</v>
+      </c>
+      <c r="AF88">
+        <v>0.0225478399734957</v>
+      </c>
+      <c r="AG88">
+        <v>154.209573001553</v>
+      </c>
+      <c r="AH88">
+        <v>253.7315612327805</v>
+      </c>
+      <c r="AI88">
+        <v>253.7315612327805</v>
+      </c>
+      <c r="AJ88">
+        <v>316.51791029734</v>
+      </c>
+      <c r="AK88">
+        <v>416.0398985285677</v>
+      </c>
+      <c r="AO88">
+        <v>-24.245</v>
+      </c>
+      <c r="AP88">
+        <v>0.012783</v>
+      </c>
+      <c r="AQ88">
+        <v>6.3725</v>
+      </c>
+      <c r="AR88">
+        <v>-25.1125</v>
+      </c>
+      <c r="AS88">
+        <v>0.02081925</v>
+      </c>
+      <c r="AT88">
+        <v>16.185</v>
+      </c>
+      <c r="AX88">
+        <v>-26.1325</v>
+      </c>
+      <c r="BB88">
+        <v>0.0014708375</v>
+      </c>
+      <c r="BC88">
+        <v>21.1825</v>
       </c>
     </row>
     <row r="89">
@@ -2543,13 +2543,10 @@
         </is>
       </c>
       <c r="B89" s="2">
-        <v>45603</v>
+        <v>45597</v>
       </c>
       <c r="F89">
-        <v>0.23</v>
-      </c>
-      <c r="BD89">
-        <v>0.01018202435546032</v>
+        <v>0.33125</v>
       </c>
     </row>
     <row r="90">
@@ -2559,13 +2556,10 @@
         </is>
       </c>
       <c r="B90" s="2">
-        <v>45604</v>
-      </c>
-      <c r="F90">
-        <v>0.165</v>
-      </c>
-      <c r="BD90">
-        <v>0.02917442495577625</v>
+        <v>45600</v>
+      </c>
+      <c r="BL90">
+        <v>10</v>
       </c>
     </row>
     <row r="91">
@@ -2575,10 +2569,13 @@
         </is>
       </c>
       <c r="B91" s="2">
-        <v>45608</v>
+        <v>45603</v>
       </c>
       <c r="F91">
-        <v>0.16375</v>
+        <v>0.23</v>
+      </c>
+      <c r="BD91">
+        <v>0.01018202435546032</v>
       </c>
     </row>
     <row r="92">
@@ -2588,10 +2585,13 @@
         </is>
       </c>
       <c r="B92" s="2">
-        <v>45610</v>
+        <v>45604</v>
+      </c>
+      <c r="F92">
+        <v>0.165</v>
       </c>
       <c r="BD92">
-        <v>0.0009194621388643045</v>
+        <v>0.02917442495577625</v>
       </c>
     </row>
     <row r="93">
@@ -2601,13 +2601,10 @@
         </is>
       </c>
       <c r="B93" s="2">
-        <v>45618</v>
-      </c>
-      <c r="BD93">
-        <v>1.396863700094107e-06</v>
-      </c>
-      <c r="BE93">
-        <v>309.8243911086972</v>
+        <v>45608</v>
+      </c>
+      <c r="F93">
+        <v>0.16375</v>
       </c>
     </row>
     <row r="94">
@@ -2617,78 +2614,10 @@
         </is>
       </c>
       <c r="B94" s="2">
-        <v>45625</v>
-      </c>
-      <c r="G94">
-        <v>773.5926041199006</v>
-      </c>
-      <c r="L94">
-        <v>8430.357933651176</v>
-      </c>
-      <c r="M94">
-        <v>322.788429386155</v>
-      </c>
-      <c r="N94">
-        <v>70.15286401018957</v>
-      </c>
-      <c r="AD94">
-        <v>111.9707572397977</v>
-      </c>
-      <c r="AE94">
-        <v>9371.916421245107</v>
-      </c>
-      <c r="AF94">
-        <v>0.03830677243008758</v>
-      </c>
-      <c r="AG94">
-        <v>358.6550835428453</v>
-      </c>
-      <c r="AH94">
-        <v>287.711681781449</v>
-      </c>
-      <c r="AI94">
-        <v>470.6258407826433</v>
-      </c>
-      <c r="AJ94">
-        <v>232.8138993270678</v>
-      </c>
-      <c r="AK94">
-        <v>344.784656566866</v>
-      </c>
-      <c r="AN94">
-        <v>318.2672373370048</v>
-      </c>
-      <c r="AO94">
-        <v>-25.43</v>
-      </c>
-      <c r="AP94">
-        <v>0.01244425</v>
-      </c>
-      <c r="AQ94">
-        <v>6.5325</v>
-      </c>
-      <c r="AX94">
-        <v>-26.1475</v>
-      </c>
-      <c r="AY94">
-        <v>-25.4825</v>
-      </c>
-      <c r="AZ94">
-        <v>0.009822600000000001</v>
-      </c>
-      <c r="BA94">
-        <v>6.17</v>
-      </c>
-      <c r="BB94">
-        <v>-0.0012263</v>
-      </c>
-      <c r="BC94">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="BK94" t="inlineStr">
-        <is>
-          <t>HarvestRipe</t>
-        </is>
+        <v>45610</v>
+      </c>
+      <c r="BD94">
+        <v>0.0009194621388643045</v>
       </c>
     </row>
     <row r="95">
@@ -2698,10 +2627,13 @@
         </is>
       </c>
       <c r="B95" s="2">
-        <v>45628</v>
+        <v>45618</v>
       </c>
       <c r="BD95">
-        <v>0</v>
+        <v>1.396863700094107e-06</v>
+      </c>
+      <c r="BE95">
+        <v>309.8243911086972</v>
       </c>
     </row>
     <row r="96">
@@ -2711,51 +2643,116 @@
         </is>
       </c>
       <c r="B96" s="2">
-        <v>45644</v>
-      </c>
-      <c r="BF96">
-        <v>72.75</v>
-      </c>
-      <c r="BG96">
-        <v>11.325</v>
-      </c>
-      <c r="BH96">
-        <v>13.2625</v>
-      </c>
-      <c r="BI96">
-        <v>0.9</v>
-      </c>
-      <c r="BJ96">
-        <v>2.917367395939084</v>
+        <v>45625</v>
+      </c>
+      <c r="G96">
+        <v>773.5926041199006</v>
+      </c>
+      <c r="L96">
+        <v>8430.357933651176</v>
+      </c>
+      <c r="M96">
+        <v>322.788429386155</v>
+      </c>
+      <c r="N96">
+        <v>70.15286401018957</v>
+      </c>
+      <c r="AD96">
+        <v>111.9707572397977</v>
+      </c>
+      <c r="AE96">
+        <v>9371.916421245107</v>
+      </c>
+      <c r="AF96">
+        <v>0.03830677243008758</v>
+      </c>
+      <c r="AG96">
+        <v>358.6550835428453</v>
+      </c>
+      <c r="AH96">
+        <v>287.711681781449</v>
+      </c>
+      <c r="AI96">
+        <v>470.6258407826433</v>
+      </c>
+      <c r="AJ96">
+        <v>232.8138993270678</v>
+      </c>
+      <c r="AK96">
+        <v>344.784656566866</v>
+      </c>
+      <c r="AN96">
+        <v>318.2672373370048</v>
+      </c>
+      <c r="AO96">
+        <v>-25.43</v>
+      </c>
+      <c r="AP96">
+        <v>0.01244425</v>
+      </c>
+      <c r="AQ96">
+        <v>6.5325</v>
+      </c>
+      <c r="AX96">
+        <v>-26.1475</v>
+      </c>
+      <c r="AY96">
+        <v>-25.4825</v>
+      </c>
+      <c r="AZ96">
+        <v>0.009822600000000001</v>
+      </c>
+      <c r="BA96">
+        <v>6.17</v>
+      </c>
+      <c r="BB96">
+        <v>-0.0012263</v>
+      </c>
+      <c r="BC96">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="BK96" t="inlineStr">
+        <is>
+          <t>HarvestRipe</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FAR VIC W24-50CvSunmaster</t>
+          <t>FAR VIC W24-50CvIllabo</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>45451</v>
-      </c>
-      <c r="BL97">
-        <v>3</v>
+        <v>45628</v>
+      </c>
+      <c r="BD97">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FAR VIC W24-50CvSunmaster</t>
+          <t>FAR VIC W24-50CvIllabo</t>
         </is>
       </c>
       <c r="B98" s="2">
-        <v>45461</v>
-      </c>
-      <c r="F98">
-        <v>0.1225</v>
-      </c>
-      <c r="Y98">
-        <v>1.5</v>
+        <v>45644</v>
+      </c>
+      <c r="BF98">
+        <v>72.75</v>
+      </c>
+      <c r="BG98">
+        <v>11.325</v>
+      </c>
+      <c r="BH98">
+        <v>13.2625</v>
+      </c>
+      <c r="BI98">
+        <v>0.9</v>
+      </c>
+      <c r="BJ98">
+        <v>2.917367395939084</v>
       </c>
     </row>
     <row r="99">
@@ -2765,10 +2762,10 @@
         </is>
       </c>
       <c r="B99" s="2">
-        <v>45467</v>
-      </c>
-      <c r="Y99">
-        <v>1.875</v>
+        <v>45451</v>
+      </c>
+      <c r="BL99">
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -2778,10 +2775,13 @@
         </is>
       </c>
       <c r="B100" s="2">
-        <v>45469</v>
-      </c>
-      <c r="BD100">
-        <v>0.03303111275718847</v>
+        <v>45461</v>
+      </c>
+      <c r="F100">
+        <v>0.1225</v>
+      </c>
+      <c r="Y100">
+        <v>1.5</v>
       </c>
     </row>
     <row r="101">
@@ -2791,13 +2791,10 @@
         </is>
       </c>
       <c r="B101" s="2">
-        <v>45474</v>
-      </c>
-      <c r="F101">
-        <v>0.2025</v>
+        <v>45467</v>
       </c>
       <c r="Y101">
-        <v>2.475000000000002</v>
+        <v>1.875</v>
       </c>
     </row>
     <row r="102">
@@ -2807,10 +2804,10 @@
         </is>
       </c>
       <c r="B102" s="2">
-        <v>45477</v>
+        <v>45469</v>
       </c>
       <c r="BD102">
-        <v>0.07212324140236376</v>
+        <v>0.03303111275718847</v>
       </c>
     </row>
     <row r="103">
@@ -2820,19 +2817,13 @@
         </is>
       </c>
       <c r="B103" s="2">
-        <v>45481</v>
-      </c>
-      <c r="C103">
-        <v>160.3239583333323</v>
-      </c>
-      <c r="D103">
-        <v>125.2777777777777</v>
-      </c>
-      <c r="E103">
-        <v>1</v>
+        <v>45474</v>
+      </c>
+      <c r="F103">
+        <v>0.2025</v>
       </c>
       <c r="Y103">
-        <v>2.933333333333333</v>
+        <v>2.475000000000002</v>
       </c>
     </row>
     <row r="104">
@@ -2842,10 +2833,10 @@
         </is>
       </c>
       <c r="B104" s="2">
-        <v>45490</v>
+        <v>45477</v>
       </c>
       <c r="BD104">
-        <v>0.08550002850034492</v>
+        <v>0.07212324140236376</v>
       </c>
     </row>
     <row r="105">
@@ -2855,10 +2846,19 @@
         </is>
       </c>
       <c r="B105" s="2">
-        <v>45499</v>
-      </c>
-      <c r="BL105">
-        <v>5</v>
+        <v>45481</v>
+      </c>
+      <c r="C105">
+        <v>160.3239583333323</v>
+      </c>
+      <c r="D105">
+        <v>125.2777777777777</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="Y105">
+        <v>2.933333333333333</v>
       </c>
     </row>
     <row r="106">
@@ -2868,19 +2868,10 @@
         </is>
       </c>
       <c r="B106" s="2">
-        <v>45502</v>
-      </c>
-      <c r="F106">
-        <v>0.2825</v>
-      </c>
-      <c r="Y106">
-        <v>4.8</v>
-      </c>
-      <c r="AM106">
-        <v>16.16666666666665</v>
-      </c>
-      <c r="BD106">
-        <v>0.165697553772076</v>
+        <v>45481</v>
+      </c>
+      <c r="BL106">
+        <v>4</v>
       </c>
     </row>
     <row r="107">
@@ -2890,10 +2881,10 @@
         </is>
       </c>
       <c r="B107" s="2">
-        <v>45506</v>
+        <v>45490</v>
       </c>
       <c r="BD107">
-        <v>0.2066729998827155</v>
+        <v>0.08550002850034492</v>
       </c>
     </row>
     <row r="108">
@@ -2903,10 +2894,19 @@
         </is>
       </c>
       <c r="B108" s="2">
-        <v>45509</v>
+        <v>45502</v>
+      </c>
+      <c r="F108">
+        <v>0.2825</v>
       </c>
       <c r="Y108">
-        <v>5.308333333333335</v>
+        <v>4.8</v>
+      </c>
+      <c r="AM108">
+        <v>16.16666666666665</v>
+      </c>
+      <c r="BD108">
+        <v>0.165697553772076</v>
       </c>
     </row>
     <row r="109">
@@ -2916,19 +2916,10 @@
         </is>
       </c>
       <c r="B109" s="2">
-        <v>45516</v>
-      </c>
-      <c r="F109">
-        <v>0.3325</v>
-      </c>
-      <c r="Y109">
-        <v>5.775</v>
-      </c>
-      <c r="AM109">
-        <v>16.66666666666667</v>
+        <v>45506</v>
       </c>
       <c r="BD109">
-        <v>0.3535373200500038</v>
+        <v>0.2066729998827155</v>
       </c>
     </row>
     <row r="110">
@@ -2938,10 +2929,10 @@
         </is>
       </c>
       <c r="B110" s="2">
-        <v>45523</v>
+        <v>45509</v>
       </c>
       <c r="Y110">
-        <v>6.574999999999998</v>
+        <v>5.308333333333335</v>
       </c>
     </row>
     <row r="111">
@@ -2951,10 +2942,19 @@
         </is>
       </c>
       <c r="B111" s="2">
-        <v>45525</v>
+        <v>45516</v>
+      </c>
+      <c r="F111">
+        <v>0.3325</v>
+      </c>
+      <c r="Y111">
+        <v>5.775</v>
+      </c>
+      <c r="AM111">
+        <v>16.66666666666667</v>
       </c>
       <c r="BD111">
-        <v>0.3912859499352442</v>
+        <v>0.3535373200500038</v>
       </c>
     </row>
     <row r="112">
@@ -2964,16 +2964,10 @@
         </is>
       </c>
       <c r="B112" s="2">
-        <v>45530</v>
-      </c>
-      <c r="F112">
-        <v>0.4475</v>
-      </c>
-      <c r="Y112">
-        <v>7.391666666666667</v>
-      </c>
-      <c r="AM112">
-        <v>27.24999999999998</v>
+        <v>45517</v>
+      </c>
+      <c r="BL112">
+        <v>5</v>
       </c>
     </row>
     <row r="113">
@@ -2983,10 +2977,10 @@
         </is>
       </c>
       <c r="B113" s="2">
-        <v>45531</v>
-      </c>
-      <c r="BD113">
-        <v>0.448853147219966</v>
+        <v>45523</v>
+      </c>
+      <c r="Y113">
+        <v>6.574999999999998</v>
       </c>
     </row>
     <row r="114">
@@ -2996,10 +2990,10 @@
         </is>
       </c>
       <c r="B114" s="2">
-        <v>45539</v>
+        <v>45525</v>
       </c>
       <c r="BD114">
-        <v>0.466073390909304</v>
+        <v>0.3912859499352442</v>
       </c>
     </row>
     <row r="115">
@@ -3009,25 +3003,16 @@
         </is>
       </c>
       <c r="B115" s="2">
-        <v>45548</v>
+        <v>45530</v>
       </c>
       <c r="F115">
-        <v>0.585</v>
-      </c>
-      <c r="H115">
-        <v>0.4327389846846325</v>
-      </c>
-      <c r="I115">
-        <v>0.3695373638445715</v>
-      </c>
-      <c r="J115">
-        <v>0.2794181952360777</v>
-      </c>
-      <c r="K115">
-        <v>0.1640476005349532</v>
+        <v>0.4475</v>
       </c>
       <c r="Y115">
-        <v>8.625</v>
+        <v>7.391666666666667</v>
+      </c>
+      <c r="AM115">
+        <v>27.24999999999998</v>
       </c>
     </row>
     <row r="116">
@@ -3037,10 +3022,10 @@
         </is>
       </c>
       <c r="B116" s="2">
-        <v>45548</v>
-      </c>
-      <c r="BL116">
-        <v>6</v>
+        <v>45531</v>
+      </c>
+      <c r="BD116">
+        <v>0.448853147219966</v>
       </c>
     </row>
     <row r="117">
@@ -3050,10 +3035,10 @@
         </is>
       </c>
       <c r="B117" s="2">
-        <v>45551</v>
-      </c>
-      <c r="AM117">
-        <v>44.75</v>
+        <v>45539</v>
+      </c>
+      <c r="BD117">
+        <v>0.466073390909304</v>
       </c>
     </row>
     <row r="118">
@@ -3063,70 +3048,25 @@
         </is>
       </c>
       <c r="B118" s="2">
-        <v>45554</v>
+        <v>45548</v>
       </c>
       <c r="F118">
-        <v>0.6425</v>
-      </c>
-      <c r="G118">
-        <v>381.7859378238305</v>
-      </c>
-      <c r="N118">
-        <v>0.119161105815062</v>
-      </c>
-      <c r="U118">
-        <v>117.154509378757</v>
-      </c>
-      <c r="Z118">
-        <v>49.825</v>
-      </c>
-      <c r="AA118">
-        <v>47.95</v>
-      </c>
-      <c r="AB118">
-        <v>51.3</v>
-      </c>
-      <c r="AC118">
-        <v>52.4</v>
-      </c>
-      <c r="AI118">
-        <v>38.94144808468403</v>
-      </c>
-      <c r="AJ118">
-        <v>225.5708192545748</v>
-      </c>
-      <c r="AL118">
-        <v>264.5122673392588</v>
-      </c>
-      <c r="AM118">
-        <v>48.08333333333333</v>
-      </c>
-      <c r="AR118">
-        <v>-24.595</v>
-      </c>
-      <c r="AS118">
-        <v>0.04284475</v>
-      </c>
-      <c r="AT118">
-        <v>10.2525</v>
-      </c>
-      <c r="AU118">
-        <v>-24.225</v>
-      </c>
-      <c r="AV118">
-        <v>0.03478125</v>
-      </c>
-      <c r="AW118">
-        <v>16.62</v>
-      </c>
-      <c r="AX118">
-        <v>-25.1475</v>
-      </c>
-      <c r="BB118">
-        <v>0.01665625</v>
-      </c>
-      <c r="BC118">
-        <v>24.07</v>
+        <v>0.585</v>
+      </c>
+      <c r="H118">
+        <v>0.4327389846846325</v>
+      </c>
+      <c r="I118">
+        <v>0.3695373638445715</v>
+      </c>
+      <c r="J118">
+        <v>0.2794181952360777</v>
+      </c>
+      <c r="K118">
+        <v>0.1640476005349532</v>
+      </c>
+      <c r="Y118">
+        <v>8.625</v>
       </c>
     </row>
     <row r="119">
@@ -3136,25 +3076,10 @@
         </is>
       </c>
       <c r="B119" s="2">
-        <v>45558</v>
-      </c>
-      <c r="F119">
-        <v>0.58375</v>
-      </c>
-      <c r="O119">
-        <v>16.66666666666665</v>
-      </c>
-      <c r="R119">
-        <v>26.66666666666667</v>
-      </c>
-      <c r="S119">
-        <v>41.25</v>
-      </c>
-      <c r="Y119">
-        <v>8.666666666666664</v>
-      </c>
-      <c r="BD119">
-        <v>0.6025679657333715</v>
+        <v>45548</v>
+      </c>
+      <c r="BL119">
+        <v>6</v>
       </c>
     </row>
     <row r="120">
@@ -3164,10 +3089,10 @@
         </is>
       </c>
       <c r="B120" s="2">
-        <v>45559</v>
-      </c>
-      <c r="BL120">
-        <v>7</v>
+        <v>45551</v>
+      </c>
+      <c r="AM120">
+        <v>44.75</v>
       </c>
     </row>
     <row r="121">
@@ -3177,10 +3102,70 @@
         </is>
       </c>
       <c r="B121" s="2">
-        <v>45565</v>
-      </c>
-      <c r="W121">
-        <v>257.217329545454</v>
+        <v>45554</v>
+      </c>
+      <c r="F121">
+        <v>0.6425</v>
+      </c>
+      <c r="G121">
+        <v>381.7859378238305</v>
+      </c>
+      <c r="N121">
+        <v>0.119161105815062</v>
+      </c>
+      <c r="U121">
+        <v>117.154509378757</v>
+      </c>
+      <c r="Z121">
+        <v>49.825</v>
+      </c>
+      <c r="AA121">
+        <v>47.95</v>
+      </c>
+      <c r="AB121">
+        <v>51.3</v>
+      </c>
+      <c r="AC121">
+        <v>52.4</v>
+      </c>
+      <c r="AI121">
+        <v>38.94144808468403</v>
+      </c>
+      <c r="AJ121">
+        <v>225.5708192545748</v>
+      </c>
+      <c r="AL121">
+        <v>264.5122673392588</v>
+      </c>
+      <c r="AM121">
+        <v>48.08333333333333</v>
+      </c>
+      <c r="AR121">
+        <v>-24.595</v>
+      </c>
+      <c r="AS121">
+        <v>0.04284475</v>
+      </c>
+      <c r="AT121">
+        <v>10.2525</v>
+      </c>
+      <c r="AU121">
+        <v>-24.225</v>
+      </c>
+      <c r="AV121">
+        <v>0.03478125</v>
+      </c>
+      <c r="AW121">
+        <v>16.62</v>
+      </c>
+      <c r="AX121">
+        <v>-25.1475</v>
+      </c>
+      <c r="BB121">
+        <v>0.01665625</v>
+      </c>
+      <c r="BC121">
+        <v>24.07</v>
       </c>
     </row>
     <row r="122">
@@ -3190,16 +3175,25 @@
         </is>
       </c>
       <c r="B122" s="2">
-        <v>45566</v>
+        <v>45558</v>
       </c>
       <c r="F122">
-        <v>0.59375</v>
-      </c>
-      <c r="P122">
-        <v>15.15833333333332</v>
-      </c>
-      <c r="Q122">
-        <v>1.470833333333335</v>
+        <v>0.58375</v>
+      </c>
+      <c r="O122">
+        <v>16.66666666666665</v>
+      </c>
+      <c r="R122">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="S122">
+        <v>41.25</v>
+      </c>
+      <c r="Y122">
+        <v>8.666666666666664</v>
+      </c>
+      <c r="BD122">
+        <v>0.6025679657333715</v>
       </c>
     </row>
     <row r="123">
@@ -3209,10 +3203,10 @@
         </is>
       </c>
       <c r="B123" s="2">
-        <v>45568</v>
-      </c>
-      <c r="BD123">
-        <v>0.6510950780876108</v>
+        <v>45559</v>
+      </c>
+      <c r="BL123">
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -3222,10 +3216,10 @@
         </is>
       </c>
       <c r="B124" s="2">
-        <v>45571</v>
-      </c>
-      <c r="BL124">
-        <v>8</v>
+        <v>45565</v>
+      </c>
+      <c r="W124">
+        <v>257.217329545454</v>
       </c>
     </row>
     <row r="125">
@@ -3235,91 +3229,16 @@
         </is>
       </c>
       <c r="B125" s="2">
-        <v>45576</v>
+        <v>45566</v>
       </c>
       <c r="F125">
-        <v>0.545</v>
-      </c>
-      <c r="G125">
-        <v>669.651839523646</v>
-      </c>
-      <c r="H125">
-        <v>0.485874138435619</v>
-      </c>
-      <c r="I125">
-        <v>0.4018891221606315</v>
-      </c>
-      <c r="J125">
-        <v>0.2591437956797295</v>
-      </c>
-      <c r="K125">
-        <v>0.1363436610535168</v>
-      </c>
-      <c r="N125">
-        <v>8.247272244334972</v>
-      </c>
-      <c r="U125">
-        <v>90.35876079042038</v>
-      </c>
-      <c r="AA125">
-        <v>54.175</v>
-      </c>
-      <c r="AB125">
-        <v>52.475</v>
-      </c>
-      <c r="AC125">
-        <v>53.15</v>
-      </c>
-      <c r="AH125">
-        <v>246.5131797707885</v>
-      </c>
-      <c r="AI125">
-        <v>159.587035986718</v>
-      </c>
-      <c r="AJ125">
-        <v>411.4587705021722</v>
-      </c>
-      <c r="AL125">
-        <v>571.0458064888902</v>
-      </c>
-      <c r="AM125">
-        <v>71.75</v>
-      </c>
-      <c r="AO125">
-        <v>-24.9925</v>
-      </c>
-      <c r="AP125">
-        <v>0.02161175</v>
-      </c>
-      <c r="AQ125">
-        <v>5.4925</v>
-      </c>
-      <c r="AR125">
-        <v>-24.51</v>
-      </c>
-      <c r="AS125">
-        <v>0.0407625</v>
-      </c>
-      <c r="AT125">
-        <v>12.11</v>
-      </c>
-      <c r="AU125">
-        <v>-24.7325</v>
-      </c>
-      <c r="AV125">
-        <v>0.0218115</v>
-      </c>
-      <c r="AW125">
-        <v>20.19</v>
-      </c>
-      <c r="AX125">
-        <v>-25.2125</v>
-      </c>
-      <c r="BB125">
-        <v>0.012289</v>
-      </c>
-      <c r="BC125">
-        <v>23.325</v>
+        <v>0.59375</v>
+      </c>
+      <c r="P125">
+        <v>15.15833333333332</v>
+      </c>
+      <c r="Q125">
+        <v>1.470833333333335</v>
       </c>
     </row>
     <row r="126">
@@ -3329,10 +3248,10 @@
         </is>
       </c>
       <c r="B126" s="2">
-        <v>45587</v>
-      </c>
-      <c r="X126">
-        <v>280.5641025641035</v>
+        <v>45568</v>
+      </c>
+      <c r="BD126">
+        <v>0.6510950780876108</v>
       </c>
     </row>
     <row r="127">
@@ -3342,10 +3261,10 @@
         </is>
       </c>
       <c r="B127" s="2">
-        <v>45590</v>
-      </c>
-      <c r="BD127">
-        <v>0.5013941371908808</v>
+        <v>45571</v>
+      </c>
+      <c r="BL127">
+        <v>8</v>
       </c>
     </row>
     <row r="128">
@@ -3355,67 +3274,91 @@
         </is>
       </c>
       <c r="B128" s="2">
-        <v>45595</v>
+        <v>45576</v>
+      </c>
+      <c r="F128">
+        <v>0.545</v>
       </c>
       <c r="G128">
-        <v>678.6701244758508</v>
+        <v>669.651839523646</v>
+      </c>
+      <c r="H128">
+        <v>0.485874138435619</v>
+      </c>
+      <c r="I128">
+        <v>0.4018891221606315</v>
+      </c>
+      <c r="J128">
+        <v>0.2591437956797295</v>
+      </c>
+      <c r="K128">
+        <v>0.1363436610535168</v>
       </c>
       <c r="N128">
-        <v>14.7231995078573</v>
+        <v>8.247272244334972</v>
       </c>
       <c r="U128">
-        <v>54.86420779879805</v>
-      </c>
-      <c r="AD128">
-        <v>101.0504468732705</v>
-      </c>
-      <c r="AE128">
-        <v>7817.869122608467</v>
-      </c>
-      <c r="AF128">
-        <v>0.0179901512095178</v>
-      </c>
-      <c r="AG128">
-        <v>139.9819370771505</v>
+        <v>90.35876079042038</v>
+      </c>
+      <c r="AA128">
+        <v>54.175</v>
+      </c>
+      <c r="AB128">
+        <v>52.475</v>
+      </c>
+      <c r="AC128">
+        <v>53.15</v>
       </c>
       <c r="AH128">
-        <v>241.032383950421</v>
+        <v>246.5131797707885</v>
       </c>
       <c r="AI128">
-        <v>241.032383950421</v>
+        <v>159.587035986718</v>
       </c>
       <c r="AJ128">
-        <v>328.245801121076</v>
-      </c>
-      <c r="AK128">
-        <v>429.2962479943465</v>
+        <v>411.4587705021722</v>
+      </c>
+      <c r="AL128">
+        <v>571.0458064888902</v>
+      </c>
+      <c r="AM128">
+        <v>71.75</v>
       </c>
       <c r="AO128">
-        <v>-24.5175</v>
+        <v>-24.9925</v>
       </c>
       <c r="AP128">
-        <v>0.013583</v>
+        <v>0.02161175</v>
       </c>
       <c r="AQ128">
-        <v>6.74</v>
+        <v>5.4925</v>
       </c>
       <c r="AR128">
-        <v>-24.96</v>
+        <v>-24.51</v>
       </c>
       <c r="AS128">
-        <v>0.02450125</v>
+        <v>0.0407625</v>
       </c>
       <c r="AT128">
-        <v>16.39</v>
+        <v>12.11</v>
+      </c>
+      <c r="AU128">
+        <v>-24.7325</v>
+      </c>
+      <c r="AV128">
+        <v>0.0218115</v>
+      </c>
+      <c r="AW128">
+        <v>20.19</v>
       </c>
       <c r="AX128">
-        <v>-26.16</v>
+        <v>-25.2125</v>
       </c>
       <c r="BB128">
-        <v>0.00213518</v>
+        <v>0.012289</v>
       </c>
       <c r="BC128">
-        <v>20.4025</v>
+        <v>23.325</v>
       </c>
     </row>
     <row r="129">
@@ -3425,10 +3368,10 @@
         </is>
       </c>
       <c r="B129" s="2">
-        <v>45597</v>
-      </c>
-      <c r="F129">
-        <v>0.4075</v>
+        <v>45587</v>
+      </c>
+      <c r="X129">
+        <v>280.5641025641035</v>
       </c>
     </row>
     <row r="130">
@@ -3438,13 +3381,10 @@
         </is>
       </c>
       <c r="B130" s="2">
-        <v>45603</v>
-      </c>
-      <c r="F130">
-        <v>0.28125</v>
+        <v>45590</v>
       </c>
       <c r="BD130">
-        <v>0.0511617631029285</v>
+        <v>0.5013941371908808</v>
       </c>
     </row>
     <row r="131">
@@ -3454,13 +3394,67 @@
         </is>
       </c>
       <c r="B131" s="2">
-        <v>45604</v>
-      </c>
-      <c r="F131">
-        <v>0.2425</v>
-      </c>
-      <c r="BD131">
-        <v>0.1146539002476297</v>
+        <v>45595</v>
+      </c>
+      <c r="G131">
+        <v>678.6701244758508</v>
+      </c>
+      <c r="N131">
+        <v>14.7231995078573</v>
+      </c>
+      <c r="U131">
+        <v>54.86420779879805</v>
+      </c>
+      <c r="AD131">
+        <v>101.0504468732705</v>
+      </c>
+      <c r="AE131">
+        <v>7817.869122608467</v>
+      </c>
+      <c r="AF131">
+        <v>0.0179901512095178</v>
+      </c>
+      <c r="AG131">
+        <v>139.9819370771505</v>
+      </c>
+      <c r="AH131">
+        <v>241.032383950421</v>
+      </c>
+      <c r="AI131">
+        <v>241.032383950421</v>
+      </c>
+      <c r="AJ131">
+        <v>328.245801121076</v>
+      </c>
+      <c r="AK131">
+        <v>429.2962479943465</v>
+      </c>
+      <c r="AO131">
+        <v>-24.5175</v>
+      </c>
+      <c r="AP131">
+        <v>0.013583</v>
+      </c>
+      <c r="AQ131">
+        <v>6.74</v>
+      </c>
+      <c r="AR131">
+        <v>-24.96</v>
+      </c>
+      <c r="AS131">
+        <v>0.02450125</v>
+      </c>
+      <c r="AT131">
+        <v>16.39</v>
+      </c>
+      <c r="AX131">
+        <v>-26.16</v>
+      </c>
+      <c r="BB131">
+        <v>0.00213518</v>
+      </c>
+      <c r="BC131">
+        <v>20.4025</v>
       </c>
     </row>
     <row r="132">
@@ -3470,10 +3464,10 @@
         </is>
       </c>
       <c r="B132" s="2">
-        <v>45607</v>
-      </c>
-      <c r="BL132">
-        <v>10</v>
+        <v>45597</v>
+      </c>
+      <c r="F132">
+        <v>0.4075</v>
       </c>
     </row>
     <row r="133">
@@ -3483,10 +3477,13 @@
         </is>
       </c>
       <c r="B133" s="2">
-        <v>45608</v>
+        <v>45603</v>
       </c>
       <c r="F133">
-        <v>0.22</v>
+        <v>0.28125</v>
+      </c>
+      <c r="BD133">
+        <v>0.0511617631029285</v>
       </c>
     </row>
     <row r="134">
@@ -3496,10 +3493,13 @@
         </is>
       </c>
       <c r="B134" s="2">
-        <v>45610</v>
+        <v>45604</v>
+      </c>
+      <c r="F134">
+        <v>0.2425</v>
       </c>
       <c r="BD134">
-        <v>0.02170883234026348</v>
+        <v>0.1146539002476297</v>
       </c>
     </row>
     <row r="135">
@@ -3509,13 +3509,10 @@
         </is>
       </c>
       <c r="B135" s="2">
-        <v>45618</v>
-      </c>
-      <c r="BD135">
-        <v>0.0001576330026980642</v>
-      </c>
-      <c r="BE135">
-        <v>316.057408774144</v>
+        <v>45607</v>
+      </c>
+      <c r="BL135">
+        <v>10</v>
       </c>
     </row>
     <row r="136">
@@ -3525,81 +3522,10 @@
         </is>
       </c>
       <c r="B136" s="2">
-        <v>45628</v>
-      </c>
-      <c r="G136">
-        <v>752.0636664560287</v>
-      </c>
-      <c r="L136">
-        <v>8889.198898635244</v>
-      </c>
-      <c r="M136">
-        <v>337.8344437417053</v>
-      </c>
-      <c r="N136">
-        <v>56.9946530949603</v>
-      </c>
-      <c r="AD136">
-        <v>101.9698860887984</v>
-      </c>
-      <c r="AE136">
-        <v>9650.680831165333</v>
-      </c>
-      <c r="AF136">
-        <v>0.0379845440770719</v>
-      </c>
-      <c r="AG136">
-        <v>366.540635687175</v>
-      </c>
-      <c r="AH136">
-        <v>251.6124190920788</v>
-      </c>
-      <c r="AI136">
-        <v>468.5105217759735</v>
-      </c>
-      <c r="AJ136">
-        <v>226.5584915850948</v>
-      </c>
-      <c r="AK136">
-        <v>328.5283776738935</v>
-      </c>
-      <c r="AN136">
-        <v>286.0568635365232</v>
-      </c>
-      <c r="AO136">
-        <v>-25.485</v>
-      </c>
-      <c r="AP136">
-        <v>0.011244925</v>
-      </c>
-      <c r="AQ136">
-        <v>6.2</v>
-      </c>
-      <c r="AX136">
-        <v>-26.0775</v>
-      </c>
-      <c r="AY136">
-        <v>-25.5425</v>
-      </c>
-      <c r="AZ136">
-        <v>0.00911125</v>
-      </c>
-      <c r="BA136">
-        <v>6.5375</v>
-      </c>
-      <c r="BB136">
-        <v>-0.0024773675</v>
-      </c>
-      <c r="BC136">
-        <v>8.914999999999999</v>
-      </c>
-      <c r="BD136">
-        <v>0</v>
-      </c>
-      <c r="BK136" t="inlineStr">
-        <is>
-          <t>HarvestRipe</t>
-        </is>
+        <v>45608</v>
+      </c>
+      <c r="F136">
+        <v>0.22</v>
       </c>
     </row>
     <row r="137">
@@ -3609,64 +3535,135 @@
         </is>
       </c>
       <c r="B137" s="2">
-        <v>45644</v>
-      </c>
-      <c r="BF137">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="BG137">
-        <v>11.6</v>
-      </c>
-      <c r="BH137">
-        <v>11.4375</v>
-      </c>
-      <c r="BI137">
-        <v>1.25</v>
-      </c>
-      <c r="BJ137">
-        <v>3.507182372604642</v>
+        <v>45610</v>
+      </c>
+      <c r="BD137">
+        <v>0.02170883234026348</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FAR VIC W24-50CvZanzibar</t>
+          <t>FAR VIC W24-50CvSunmaster</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>45449</v>
-      </c>
-      <c r="BL138">
-        <v>3</v>
+        <v>45618</v>
+      </c>
+      <c r="BD138">
+        <v>0.0001576330026980642</v>
+      </c>
+      <c r="BE138">
+        <v>316.057408774144</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FAR VIC W24-50CvZanzibar</t>
+          <t>FAR VIC W24-50CvSunmaster</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>45461</v>
-      </c>
-      <c r="F139">
-        <v>0.1225</v>
-      </c>
-      <c r="Y139">
-        <v>1.550000000000002</v>
+        <v>45628</v>
+      </c>
+      <c r="G139">
+        <v>752.0636664560287</v>
+      </c>
+      <c r="L139">
+        <v>8889.198898635244</v>
+      </c>
+      <c r="M139">
+        <v>337.8344437417053</v>
+      </c>
+      <c r="N139">
+        <v>56.9946530949603</v>
+      </c>
+      <c r="AD139">
+        <v>101.9698860887984</v>
+      </c>
+      <c r="AE139">
+        <v>9650.680831165333</v>
+      </c>
+      <c r="AF139">
+        <v>0.0379845440770719</v>
+      </c>
+      <c r="AG139">
+        <v>366.540635687175</v>
+      </c>
+      <c r="AH139">
+        <v>251.6124190920788</v>
+      </c>
+      <c r="AI139">
+        <v>468.5105217759735</v>
+      </c>
+      <c r="AJ139">
+        <v>226.5584915850948</v>
+      </c>
+      <c r="AK139">
+        <v>328.5283776738935</v>
+      </c>
+      <c r="AN139">
+        <v>286.0568635365232</v>
+      </c>
+      <c r="AO139">
+        <v>-25.485</v>
+      </c>
+      <c r="AP139">
+        <v>0.011244925</v>
+      </c>
+      <c r="AQ139">
+        <v>6.2</v>
+      </c>
+      <c r="AX139">
+        <v>-26.0775</v>
+      </c>
+      <c r="AY139">
+        <v>-25.5425</v>
+      </c>
+      <c r="AZ139">
+        <v>0.00911125</v>
+      </c>
+      <c r="BA139">
+        <v>6.5375</v>
+      </c>
+      <c r="BB139">
+        <v>-0.0024773675</v>
+      </c>
+      <c r="BC139">
+        <v>8.914999999999999</v>
+      </c>
+      <c r="BD139">
+        <v>0</v>
+      </c>
+      <c r="BK139" t="inlineStr">
+        <is>
+          <t>HarvestRipe</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FAR VIC W24-50CvZanzibar</t>
+          <t>FAR VIC W24-50CvSunmaster</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>45467</v>
-      </c>
-      <c r="Y140">
-        <v>1.966666666666667</v>
+        <v>45644</v>
+      </c>
+      <c r="BF140">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="BG140">
+        <v>11.6</v>
+      </c>
+      <c r="BH140">
+        <v>11.4375</v>
+      </c>
+      <c r="BI140">
+        <v>1.25</v>
+      </c>
+      <c r="BJ140">
+        <v>3.507182372604642</v>
       </c>
     </row>
     <row r="141">
@@ -3676,10 +3673,10 @@
         </is>
       </c>
       <c r="B141" s="2">
-        <v>45469</v>
-      </c>
-      <c r="BD141">
-        <v>0.02503884704651661</v>
+        <v>45449</v>
+      </c>
+      <c r="BL141">
+        <v>3</v>
       </c>
     </row>
     <row r="142">
@@ -3689,13 +3686,13 @@
         </is>
       </c>
       <c r="B142" s="2">
-        <v>45474</v>
+        <v>45461</v>
       </c>
       <c r="F142">
-        <v>0.2075</v>
+        <v>0.1225</v>
       </c>
       <c r="Y142">
-        <v>2.441666666666667</v>
+        <v>1.550000000000002</v>
       </c>
     </row>
     <row r="143">
@@ -3705,10 +3702,10 @@
         </is>
       </c>
       <c r="B143" s="2">
-        <v>45477</v>
-      </c>
-      <c r="BD143">
-        <v>0.03512519171269735</v>
+        <v>45467</v>
+      </c>
+      <c r="Y143">
+        <v>1.966666666666667</v>
       </c>
     </row>
     <row r="144">
@@ -3718,19 +3715,10 @@
         </is>
       </c>
       <c r="B144" s="2">
-        <v>45481</v>
-      </c>
-      <c r="C144">
-        <v>158.8748233275</v>
-      </c>
-      <c r="D144">
-        <v>95.0000000000001</v>
-      </c>
-      <c r="E144">
-        <v>0.939655172413793</v>
-      </c>
-      <c r="Y144">
-        <v>3.05</v>
+        <v>45469</v>
+      </c>
+      <c r="BD144">
+        <v>0.02503884704651661</v>
       </c>
     </row>
     <row r="145">
@@ -3740,10 +3728,13 @@
         </is>
       </c>
       <c r="B145" s="2">
-        <v>45490</v>
-      </c>
-      <c r="BD145">
-        <v>0.03619204814994735</v>
+        <v>45474</v>
+      </c>
+      <c r="F145">
+        <v>0.2075</v>
+      </c>
+      <c r="Y145">
+        <v>2.441666666666667</v>
       </c>
     </row>
     <row r="146">
@@ -3753,19 +3744,10 @@
         </is>
       </c>
       <c r="B146" s="2">
-        <v>45502</v>
-      </c>
-      <c r="F146">
-        <v>0.265</v>
-      </c>
-      <c r="Y146">
-        <v>5.15</v>
-      </c>
-      <c r="AM146">
-        <v>13.33333333333333</v>
+        <v>45477</v>
       </c>
       <c r="BD146">
-        <v>0.1732586408202815</v>
+        <v>0.03512519171269735</v>
       </c>
     </row>
     <row r="147">
@@ -3775,10 +3757,19 @@
         </is>
       </c>
       <c r="B147" s="2">
-        <v>45502</v>
-      </c>
-      <c r="BL147">
-        <v>5</v>
+        <v>45481</v>
+      </c>
+      <c r="C147">
+        <v>158.8748233275</v>
+      </c>
+      <c r="D147">
+        <v>95.0000000000001</v>
+      </c>
+      <c r="E147">
+        <v>0.939655172413793</v>
+      </c>
+      <c r="Y147">
+        <v>3.05</v>
       </c>
     </row>
     <row r="148">
@@ -3788,10 +3779,10 @@
         </is>
       </c>
       <c r="B148" s="2">
-        <v>45506</v>
+        <v>45490</v>
       </c>
       <c r="BD148">
-        <v>0.186505792966201</v>
+        <v>0.03619204814994735</v>
       </c>
     </row>
     <row r="149">
@@ -3801,10 +3792,10 @@
         </is>
       </c>
       <c r="B149" s="2">
-        <v>45509</v>
-      </c>
-      <c r="Y149">
-        <v>5.666666666666665</v>
+        <v>45490</v>
+      </c>
+      <c r="BL149">
+        <v>4</v>
       </c>
     </row>
     <row r="150">
@@ -3814,19 +3805,19 @@
         </is>
       </c>
       <c r="B150" s="2">
-        <v>45516</v>
+        <v>45502</v>
       </c>
       <c r="F150">
-        <v>0.345</v>
+        <v>0.265</v>
       </c>
       <c r="Y150">
-        <v>6.241666666666667</v>
+        <v>5.15</v>
       </c>
       <c r="AM150">
-        <v>12.83333333333333</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="BD150">
-        <v>0.219096926365689</v>
+        <v>0.1732586408202815</v>
       </c>
     </row>
     <row r="151">
@@ -3836,10 +3827,10 @@
         </is>
       </c>
       <c r="B151" s="2">
-        <v>45523</v>
-      </c>
-      <c r="Y151">
-        <v>7.05</v>
+        <v>45506</v>
+      </c>
+      <c r="BD151">
+        <v>0.186505792966201</v>
       </c>
     </row>
     <row r="152">
@@ -3849,10 +3840,10 @@
         </is>
       </c>
       <c r="B152" s="2">
-        <v>45525</v>
-      </c>
-      <c r="BD152">
-        <v>0.3894019324731893</v>
+        <v>45509</v>
+      </c>
+      <c r="Y152">
+        <v>5.666666666666665</v>
       </c>
     </row>
     <row r="153">
@@ -3862,16 +3853,19 @@
         </is>
       </c>
       <c r="B153" s="2">
-        <v>45530</v>
+        <v>45516</v>
       </c>
       <c r="F153">
-        <v>0.45</v>
+        <v>0.345</v>
       </c>
       <c r="Y153">
-        <v>7.891666666666665</v>
+        <v>6.241666666666667</v>
       </c>
       <c r="AM153">
-        <v>22.83333333333335</v>
+        <v>12.83333333333333</v>
+      </c>
+      <c r="BD153">
+        <v>0.219096926365689</v>
       </c>
     </row>
     <row r="154">
@@ -3881,10 +3875,10 @@
         </is>
       </c>
       <c r="B154" s="2">
-        <v>45531</v>
-      </c>
-      <c r="BD154">
-        <v>0.446535261148474</v>
+        <v>45522</v>
+      </c>
+      <c r="BL154">
+        <v>5</v>
       </c>
     </row>
     <row r="155">
@@ -3894,10 +3888,10 @@
         </is>
       </c>
       <c r="B155" s="2">
-        <v>45539</v>
-      </c>
-      <c r="BD155">
-        <v>0.414522106856422</v>
+        <v>45523</v>
+      </c>
+      <c r="Y155">
+        <v>7.05</v>
       </c>
     </row>
     <row r="156">
@@ -3907,25 +3901,10 @@
         </is>
       </c>
       <c r="B156" s="2">
-        <v>45548</v>
-      </c>
-      <c r="F156">
-        <v>0.5825</v>
-      </c>
-      <c r="H156">
-        <v>0.3861458096345797</v>
-      </c>
-      <c r="I156">
-        <v>0.3166544797522575</v>
-      </c>
-      <c r="J156">
-        <v>0.2118595720644842</v>
-      </c>
-      <c r="K156">
-        <v>0.105858820180095</v>
-      </c>
-      <c r="Y156">
-        <v>9.641666666666666</v>
+        <v>45525</v>
+      </c>
+      <c r="BD156">
+        <v>0.3894019324731893</v>
       </c>
     </row>
     <row r="157">
@@ -3935,10 +3914,16 @@
         </is>
       </c>
       <c r="B157" s="2">
-        <v>45551</v>
+        <v>45530</v>
+      </c>
+      <c r="F157">
+        <v>0.45</v>
+      </c>
+      <c r="Y157">
+        <v>7.891666666666665</v>
       </c>
       <c r="AM157">
-        <v>43.33333333333335</v>
+        <v>22.83333333333335</v>
       </c>
     </row>
     <row r="158">
@@ -3948,10 +3933,10 @@
         </is>
       </c>
       <c r="B158" s="2">
-        <v>45554</v>
-      </c>
-      <c r="AM158">
-        <v>45.41666666666665</v>
+        <v>45531</v>
+      </c>
+      <c r="BD158">
+        <v>0.446535261148474</v>
       </c>
     </row>
     <row r="159">
@@ -3961,10 +3946,10 @@
         </is>
       </c>
       <c r="B159" s="2">
-        <v>45556</v>
-      </c>
-      <c r="BL159">
-        <v>6</v>
+        <v>45539</v>
+      </c>
+      <c r="BD159">
+        <v>0.414522106856422</v>
       </c>
     </row>
     <row r="160">
@@ -3974,25 +3959,25 @@
         </is>
       </c>
       <c r="B160" s="2">
-        <v>45558</v>
+        <v>45548</v>
       </c>
       <c r="F160">
-        <v>0.60375</v>
-      </c>
-      <c r="O160">
-        <v>2.916666666666665</v>
-      </c>
-      <c r="R160">
-        <v>26.66666666666667</v>
-      </c>
-      <c r="S160">
-        <v>33.75</v>
+        <v>0.5825</v>
+      </c>
+      <c r="H160">
+        <v>0.3861458096345797</v>
+      </c>
+      <c r="I160">
+        <v>0.3166544797522575</v>
+      </c>
+      <c r="J160">
+        <v>0.2118595720644842</v>
+      </c>
+      <c r="K160">
+        <v>0.105858820180095</v>
       </c>
       <c r="Y160">
-        <v>9.999999999999982</v>
-      </c>
-      <c r="BD160">
-        <v>0.6113665761468683</v>
+        <v>9.641666666666666</v>
       </c>
     </row>
     <row r="161">
@@ -4002,70 +3987,10 @@
         </is>
       </c>
       <c r="B161" s="2">
-        <v>45561</v>
-      </c>
-      <c r="F161">
-        <v>0.7025</v>
-      </c>
-      <c r="G161">
-        <v>475.7601326145723</v>
-      </c>
-      <c r="N161">
-        <v>0.1733038749400817</v>
-      </c>
-      <c r="U161">
-        <v>103.5302771778961</v>
-      </c>
-      <c r="Z161">
-        <v>55.90000000000001</v>
-      </c>
-      <c r="AA161">
-        <v>56.1</v>
-      </c>
-      <c r="AB161">
-        <v>57.7</v>
-      </c>
-      <c r="AC161">
-        <v>57.625</v>
-      </c>
-      <c r="AI161">
-        <v>79.59422320875285</v>
-      </c>
-      <c r="AJ161">
-        <v>292.4623283529833</v>
-      </c>
-      <c r="AL161">
-        <v>372.056551561736</v>
+        <v>45551</v>
       </c>
       <c r="AM161">
-        <v>65.75</v>
-      </c>
-      <c r="AR161">
-        <v>-24.7575</v>
-      </c>
-      <c r="AS161">
-        <v>0.04568975</v>
-      </c>
-      <c r="AT161">
-        <v>8.307499999999999</v>
-      </c>
-      <c r="AU161">
-        <v>-24.6025</v>
-      </c>
-      <c r="AV161">
-        <v>0.02188725</v>
-      </c>
-      <c r="AW161">
-        <v>17.465</v>
-      </c>
-      <c r="AX161">
-        <v>-25</v>
-      </c>
-      <c r="BB161">
-        <v>0.01802625</v>
-      </c>
-      <c r="BC161">
-        <v>19.7475</v>
+        <v>43.33333333333335</v>
       </c>
     </row>
     <row r="162">
@@ -4075,10 +4000,10 @@
         </is>
       </c>
       <c r="B162" s="2">
-        <v>45565</v>
-      </c>
-      <c r="W162">
-        <v>265.0465811965807</v>
+        <v>45554</v>
+      </c>
+      <c r="AM162">
+        <v>45.41666666666665</v>
       </c>
     </row>
     <row r="163">
@@ -4088,10 +4013,10 @@
         </is>
       </c>
       <c r="B163" s="2">
-        <v>45565</v>
+        <v>45556</v>
       </c>
       <c r="BL163">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164">
@@ -4101,16 +4026,25 @@
         </is>
       </c>
       <c r="B164" s="2">
-        <v>45566</v>
+        <v>45558</v>
       </c>
       <c r="F164">
-        <v>0.6125</v>
-      </c>
-      <c r="P164">
-        <v>14.16666666666667</v>
-      </c>
-      <c r="Q164">
-        <v>1.495833333333335</v>
+        <v>0.60375</v>
+      </c>
+      <c r="O164">
+        <v>2.916666666666665</v>
+      </c>
+      <c r="R164">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="S164">
+        <v>33.75</v>
+      </c>
+      <c r="Y164">
+        <v>9.999999999999982</v>
+      </c>
+      <c r="BD164">
+        <v>0.6113665761468683</v>
       </c>
     </row>
     <row r="165">
@@ -4120,10 +4054,70 @@
         </is>
       </c>
       <c r="B165" s="2">
-        <v>45568</v>
-      </c>
-      <c r="BD165">
-        <v>0.6358369612292449</v>
+        <v>45561</v>
+      </c>
+      <c r="F165">
+        <v>0.7025</v>
+      </c>
+      <c r="G165">
+        <v>475.7601326145723</v>
+      </c>
+      <c r="N165">
+        <v>0.1733038749400817</v>
+      </c>
+      <c r="U165">
+        <v>103.5302771778961</v>
+      </c>
+      <c r="Z165">
+        <v>55.90000000000001</v>
+      </c>
+      <c r="AA165">
+        <v>56.1</v>
+      </c>
+      <c r="AB165">
+        <v>57.7</v>
+      </c>
+      <c r="AC165">
+        <v>57.625</v>
+      </c>
+      <c r="AI165">
+        <v>79.59422320875285</v>
+      </c>
+      <c r="AJ165">
+        <v>292.4623283529833</v>
+      </c>
+      <c r="AL165">
+        <v>372.056551561736</v>
+      </c>
+      <c r="AM165">
+        <v>65.75</v>
+      </c>
+      <c r="AR165">
+        <v>-24.7575</v>
+      </c>
+      <c r="AS165">
+        <v>0.04568975</v>
+      </c>
+      <c r="AT165">
+        <v>8.307499999999999</v>
+      </c>
+      <c r="AU165">
+        <v>-24.6025</v>
+      </c>
+      <c r="AV165">
+        <v>0.02188725</v>
+      </c>
+      <c r="AW165">
+        <v>17.465</v>
+      </c>
+      <c r="AX165">
+        <v>-25</v>
+      </c>
+      <c r="BB165">
+        <v>0.01802625</v>
+      </c>
+      <c r="BC165">
+        <v>19.7475</v>
       </c>
     </row>
     <row r="166">
@@ -4133,25 +4127,10 @@
         </is>
       </c>
       <c r="B166" s="2">
-        <v>45569</v>
-      </c>
-      <c r="F166">
-        <v>0.6725</v>
-      </c>
-      <c r="H166">
-        <v>0.4207850752222297</v>
-      </c>
-      <c r="I166">
-        <v>0.3856436136506928</v>
-      </c>
-      <c r="J166">
-        <v>0.2995368833982425</v>
-      </c>
-      <c r="K166">
-        <v>0.1921173195173513</v>
-      </c>
-      <c r="AM166">
-        <v>73.25</v>
+        <v>45565</v>
+      </c>
+      <c r="W166">
+        <v>265.0465811965807</v>
       </c>
     </row>
     <row r="167">
@@ -4161,10 +4140,10 @@
         </is>
       </c>
       <c r="B167" s="2">
-        <v>45575</v>
+        <v>45565</v>
       </c>
       <c r="BL167">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168">
@@ -4174,91 +4153,16 @@
         </is>
       </c>
       <c r="B168" s="2">
-        <v>45576</v>
+        <v>45566</v>
       </c>
       <c r="F168">
-        <v>0.59</v>
-      </c>
-      <c r="G168">
-        <v>681.2476630983156</v>
-      </c>
-      <c r="H168">
-        <v>0.523070436325839</v>
-      </c>
-      <c r="I168">
-        <v>0.463238544834997</v>
-      </c>
-      <c r="J168">
-        <v>0.3312979478204948</v>
-      </c>
-      <c r="K168">
-        <v>0.1974197867093397</v>
-      </c>
-      <c r="N168">
-        <v>5.76828778085229</v>
-      </c>
-      <c r="U168">
-        <v>97.0693125170562</v>
-      </c>
-      <c r="AA168">
-        <v>56.45</v>
-      </c>
-      <c r="AB168">
-        <v>58.85</v>
-      </c>
-      <c r="AC168">
-        <v>52.075</v>
-      </c>
-      <c r="AH168">
-        <v>230.92407860802</v>
-      </c>
-      <c r="AI168">
-        <v>153.909873775685</v>
-      </c>
-      <c r="AJ168">
-        <v>424.500189024722</v>
-      </c>
-      <c r="AL168">
-        <v>578.4100628004073</v>
-      </c>
-      <c r="AM168">
-        <v>72.75</v>
-      </c>
-      <c r="AO168">
-        <v>-24.8725</v>
-      </c>
-      <c r="AP168">
-        <v>0.02432675</v>
-      </c>
-      <c r="AQ168">
-        <v>5.1925</v>
-      </c>
-      <c r="AR168">
-        <v>-24.9025</v>
-      </c>
-      <c r="AS168">
-        <v>0.0414095</v>
-      </c>
-      <c r="AT168">
-        <v>10.11</v>
-      </c>
-      <c r="AU168">
-        <v>-24.5875</v>
-      </c>
-      <c r="AV168">
-        <v>0.0226245</v>
-      </c>
-      <c r="AW168">
-        <v>20.725</v>
-      </c>
-      <c r="AX168">
-        <v>-24.9475</v>
-      </c>
-      <c r="BB168">
-        <v>0.01710625</v>
-      </c>
-      <c r="BC168">
-        <v>22.555</v>
+        <v>0.6125</v>
+      </c>
+      <c r="P168">
+        <v>14.16666666666667</v>
+      </c>
+      <c r="Q168">
+        <v>1.495833333333335</v>
       </c>
     </row>
     <row r="169">
@@ -4268,10 +4172,10 @@
         </is>
       </c>
       <c r="B169" s="2">
-        <v>45587</v>
-      </c>
-      <c r="X169">
-        <v>284.1812499999997</v>
+        <v>45568</v>
+      </c>
+      <c r="BD169">
+        <v>0.6358369612292449</v>
       </c>
     </row>
     <row r="170">
@@ -4281,10 +4185,25 @@
         </is>
       </c>
       <c r="B170" s="2">
-        <v>45590</v>
-      </c>
-      <c r="BD170">
-        <v>0.5530545094860505</v>
+        <v>45569</v>
+      </c>
+      <c r="F170">
+        <v>0.6725</v>
+      </c>
+      <c r="H170">
+        <v>0.4207850752222297</v>
+      </c>
+      <c r="I170">
+        <v>0.3856436136506928</v>
+      </c>
+      <c r="J170">
+        <v>0.2995368833982425</v>
+      </c>
+      <c r="K170">
+        <v>0.1921173195173513</v>
+      </c>
+      <c r="AM170">
+        <v>73.25</v>
       </c>
     </row>
     <row r="171">
@@ -4294,67 +4213,10 @@
         </is>
       </c>
       <c r="B171" s="2">
-        <v>45595</v>
-      </c>
-      <c r="G171">
-        <v>710.9754661927483</v>
-      </c>
-      <c r="N171">
-        <v>6.284010862301445</v>
-      </c>
-      <c r="U171">
-        <v>77.84603832822988</v>
-      </c>
-      <c r="AD171">
-        <v>137.6001226514157</v>
-      </c>
-      <c r="AE171">
-        <v>7777.762484037085</v>
-      </c>
-      <c r="AF171">
-        <v>0.01419682508710583</v>
-      </c>
-      <c r="AG171">
-        <v>109.0805101258183</v>
-      </c>
-      <c r="AH171">
-        <v>246.6806327772343</v>
-      </c>
-      <c r="AI171">
-        <v>246.6806327772343</v>
-      </c>
-      <c r="AJ171">
-        <v>376.6811475659263</v>
-      </c>
-      <c r="AK171">
-        <v>514.281270217342</v>
-      </c>
-      <c r="AO171">
-        <v>-24.1075</v>
-      </c>
-      <c r="AP171">
-        <v>0.01694</v>
-      </c>
-      <c r="AQ171">
-        <v>5.535</v>
-      </c>
-      <c r="AR171">
-        <v>-25.165</v>
-      </c>
-      <c r="AS171">
-        <v>0.02902075</v>
-      </c>
-      <c r="AT171">
-        <v>15.94</v>
-      </c>
-      <c r="AX171">
-        <v>-25.9275</v>
-      </c>
-      <c r="BB171">
-        <v>0.005504625</v>
-      </c>
-      <c r="BC171">
-        <v>22.7525</v>
+        <v>45575</v>
+      </c>
+      <c r="BL171">
+        <v>8</v>
       </c>
     </row>
     <row r="172">
@@ -4364,10 +4226,91 @@
         </is>
       </c>
       <c r="B172" s="2">
-        <v>45597</v>
+        <v>45576</v>
       </c>
       <c r="F172">
-        <v>0.47625</v>
+        <v>0.59</v>
+      </c>
+      <c r="G172">
+        <v>681.2476630983156</v>
+      </c>
+      <c r="H172">
+        <v>0.523070436325839</v>
+      </c>
+      <c r="I172">
+        <v>0.463238544834997</v>
+      </c>
+      <c r="J172">
+        <v>0.3312979478204948</v>
+      </c>
+      <c r="K172">
+        <v>0.1974197867093397</v>
+      </c>
+      <c r="N172">
+        <v>5.76828778085229</v>
+      </c>
+      <c r="U172">
+        <v>97.0693125170562</v>
+      </c>
+      <c r="AA172">
+        <v>56.45</v>
+      </c>
+      <c r="AB172">
+        <v>58.85</v>
+      </c>
+      <c r="AC172">
+        <v>52.075</v>
+      </c>
+      <c r="AH172">
+        <v>230.92407860802</v>
+      </c>
+      <c r="AI172">
+        <v>153.909873775685</v>
+      </c>
+      <c r="AJ172">
+        <v>424.500189024722</v>
+      </c>
+      <c r="AL172">
+        <v>578.4100628004073</v>
+      </c>
+      <c r="AM172">
+        <v>72.75</v>
+      </c>
+      <c r="AO172">
+        <v>-24.8725</v>
+      </c>
+      <c r="AP172">
+        <v>0.02432675</v>
+      </c>
+      <c r="AQ172">
+        <v>5.1925</v>
+      </c>
+      <c r="AR172">
+        <v>-24.9025</v>
+      </c>
+      <c r="AS172">
+        <v>0.0414095</v>
+      </c>
+      <c r="AT172">
+        <v>10.11</v>
+      </c>
+      <c r="AU172">
+        <v>-24.5875</v>
+      </c>
+      <c r="AV172">
+        <v>0.0226245</v>
+      </c>
+      <c r="AW172">
+        <v>20.725</v>
+      </c>
+      <c r="AX172">
+        <v>-24.9475</v>
+      </c>
+      <c r="BB172">
+        <v>0.01710625</v>
+      </c>
+      <c r="BC172">
+        <v>22.555</v>
       </c>
     </row>
     <row r="173">
@@ -4377,13 +4320,10 @@
         </is>
       </c>
       <c r="B173" s="2">
-        <v>45603</v>
-      </c>
-      <c r="F173">
-        <v>0.3625</v>
-      </c>
-      <c r="BD173">
-        <v>0.1834221799746025</v>
+        <v>45587</v>
+      </c>
+      <c r="X173">
+        <v>284.1812499999997</v>
       </c>
     </row>
     <row r="174">
@@ -4393,13 +4333,10 @@
         </is>
       </c>
       <c r="B174" s="2">
-        <v>45604</v>
-      </c>
-      <c r="F174">
-        <v>0.3325</v>
+        <v>45590</v>
       </c>
       <c r="BD174">
-        <v>0.1580857081344415</v>
+        <v>0.5530545094860505</v>
       </c>
     </row>
     <row r="175">
@@ -4409,10 +4346,67 @@
         </is>
       </c>
       <c r="B175" s="2">
-        <v>45608</v>
-      </c>
-      <c r="F175">
-        <v>0.26375</v>
+        <v>45595</v>
+      </c>
+      <c r="G175">
+        <v>710.9754661927483</v>
+      </c>
+      <c r="N175">
+        <v>6.284010862301445</v>
+      </c>
+      <c r="U175">
+        <v>77.84603832822988</v>
+      </c>
+      <c r="AD175">
+        <v>137.6001226514157</v>
+      </c>
+      <c r="AE175">
+        <v>7777.762484037085</v>
+      </c>
+      <c r="AF175">
+        <v>0.01419682508710583</v>
+      </c>
+      <c r="AG175">
+        <v>109.0805101258183</v>
+      </c>
+      <c r="AH175">
+        <v>246.6806327772343</v>
+      </c>
+      <c r="AI175">
+        <v>246.6806327772343</v>
+      </c>
+      <c r="AJ175">
+        <v>376.6811475659263</v>
+      </c>
+      <c r="AK175">
+        <v>514.281270217342</v>
+      </c>
+      <c r="AO175">
+        <v>-24.1075</v>
+      </c>
+      <c r="AP175">
+        <v>0.01694</v>
+      </c>
+      <c r="AQ175">
+        <v>5.535</v>
+      </c>
+      <c r="AR175">
+        <v>-25.165</v>
+      </c>
+      <c r="AS175">
+        <v>0.02902075</v>
+      </c>
+      <c r="AT175">
+        <v>15.94</v>
+      </c>
+      <c r="AX175">
+        <v>-25.9275</v>
+      </c>
+      <c r="BB175">
+        <v>0.005504625</v>
+      </c>
+      <c r="BC175">
+        <v>22.7525</v>
       </c>
     </row>
     <row r="176">
@@ -4422,10 +4416,10 @@
         </is>
       </c>
       <c r="B176" s="2">
-        <v>45610</v>
-      </c>
-      <c r="BD176">
-        <v>0.04900684167563</v>
+        <v>45597</v>
+      </c>
+      <c r="F176">
+        <v>0.47625</v>
       </c>
     </row>
     <row r="177">
@@ -4435,10 +4429,13 @@
         </is>
       </c>
       <c r="B177" s="2">
-        <v>45610</v>
-      </c>
-      <c r="BL177">
-        <v>10</v>
+        <v>45603</v>
+      </c>
+      <c r="F177">
+        <v>0.3625</v>
+      </c>
+      <c r="BD177">
+        <v>0.1834221799746025</v>
       </c>
     </row>
     <row r="178">
@@ -4448,13 +4445,13 @@
         </is>
       </c>
       <c r="B178" s="2">
-        <v>45618</v>
+        <v>45604</v>
+      </c>
+      <c r="F178">
+        <v>0.3325</v>
       </c>
       <c r="BD178">
-        <v>8.978008963894368e-06</v>
-      </c>
-      <c r="BE178">
-        <v>319.701493639157</v>
+        <v>0.1580857081344415</v>
       </c>
     </row>
     <row r="179">
@@ -4464,81 +4461,10 @@
         </is>
       </c>
       <c r="B179" s="2">
-        <v>45628</v>
-      </c>
-      <c r="G179">
-        <v>842.8533333256539</v>
-      </c>
-      <c r="L179">
-        <v>7997.638782819165</v>
-      </c>
-      <c r="M179">
-        <v>370.0844646988778</v>
-      </c>
-      <c r="N179">
-        <v>70.94500709233864</v>
-      </c>
-      <c r="AD179">
-        <v>110.1270634174651</v>
-      </c>
-      <c r="AE179">
-        <v>9103.826099009513</v>
-      </c>
-      <c r="AF179">
-        <v>0.04649229469722395</v>
-      </c>
-      <c r="AG179">
-        <v>421.8064878486792</v>
-      </c>
-      <c r="AH179">
-        <v>249.436086126113</v>
-      </c>
-      <c r="AI179">
-        <v>531.9335512661443</v>
-      </c>
-      <c r="AJ179">
-        <v>239.974774967171</v>
-      </c>
-      <c r="AK179">
-        <v>350.101838384636</v>
-      </c>
-      <c r="AN179">
-        <v>302.2138639038907</v>
-      </c>
-      <c r="AO179">
-        <v>-25.7225</v>
-      </c>
-      <c r="AP179">
-        <v>0.0124295</v>
-      </c>
-      <c r="AQ179">
-        <v>7.195</v>
-      </c>
-      <c r="AX179">
-        <v>-26.035</v>
-      </c>
-      <c r="AY179">
-        <v>-25.61</v>
-      </c>
-      <c r="AZ179">
-        <v>0.009700500000000001</v>
-      </c>
-      <c r="BA179">
-        <v>6.3425</v>
-      </c>
-      <c r="BB179">
-        <v>-0.0017543065</v>
-      </c>
-      <c r="BC179">
-        <v>9.1</v>
-      </c>
-      <c r="BD179">
-        <v>1.725957713981403e-05</v>
-      </c>
-      <c r="BK179" t="inlineStr">
-        <is>
-          <t>HarvestRipe</t>
-        </is>
+        <v>45608</v>
+      </c>
+      <c r="F179">
+        <v>0.26375</v>
       </c>
     </row>
     <row r="180">
@@ -4548,21 +4474,147 @@
         </is>
       </c>
       <c r="B180" s="2">
+        <v>45610</v>
+      </c>
+      <c r="BD180">
+        <v>0.04900684167563</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>FAR VIC W24-50CvZanzibar</t>
+        </is>
+      </c>
+      <c r="B181" s="2">
+        <v>45610</v>
+      </c>
+      <c r="BL181">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>FAR VIC W24-50CvZanzibar</t>
+        </is>
+      </c>
+      <c r="B182" s="2">
+        <v>45618</v>
+      </c>
+      <c r="BD182">
+        <v>8.978008963894368e-06</v>
+      </c>
+      <c r="BE182">
+        <v>319.701493639157</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>FAR VIC W24-50CvZanzibar</t>
+        </is>
+      </c>
+      <c r="B183" s="2">
+        <v>45628</v>
+      </c>
+      <c r="G183">
+        <v>842.8533333256539</v>
+      </c>
+      <c r="L183">
+        <v>7997.638782819165</v>
+      </c>
+      <c r="M183">
+        <v>370.0844646988778</v>
+      </c>
+      <c r="N183">
+        <v>70.94500709233864</v>
+      </c>
+      <c r="AD183">
+        <v>110.1270634174651</v>
+      </c>
+      <c r="AE183">
+        <v>9103.826099009513</v>
+      </c>
+      <c r="AF183">
+        <v>0.04649229469722395</v>
+      </c>
+      <c r="AG183">
+        <v>421.8064878486792</v>
+      </c>
+      <c r="AH183">
+        <v>249.436086126113</v>
+      </c>
+      <c r="AI183">
+        <v>531.9335512661443</v>
+      </c>
+      <c r="AJ183">
+        <v>239.974774967171</v>
+      </c>
+      <c r="AK183">
+        <v>350.101838384636</v>
+      </c>
+      <c r="AN183">
+        <v>302.2138639038907</v>
+      </c>
+      <c r="AO183">
+        <v>-25.7225</v>
+      </c>
+      <c r="AP183">
+        <v>0.0124295</v>
+      </c>
+      <c r="AQ183">
+        <v>7.195</v>
+      </c>
+      <c r="AX183">
+        <v>-26.035</v>
+      </c>
+      <c r="AY183">
+        <v>-25.61</v>
+      </c>
+      <c r="AZ183">
+        <v>0.009700500000000001</v>
+      </c>
+      <c r="BA183">
+        <v>6.3425</v>
+      </c>
+      <c r="BB183">
+        <v>-0.0017543065</v>
+      </c>
+      <c r="BC183">
+        <v>9.1</v>
+      </c>
+      <c r="BD183">
+        <v>1.725957713981403e-05</v>
+      </c>
+      <c r="BK183" t="inlineStr">
+        <is>
+          <t>HarvestRipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>FAR VIC W24-50CvZanzibar</t>
+        </is>
+      </c>
+      <c r="B184" s="2">
         <v>45644</v>
       </c>
-      <c r="BF180">
+      <c r="BF184">
         <v>76.925</v>
       </c>
-      <c r="BG180">
+      <c r="BG184">
         <v>11.3625</v>
       </c>
-      <c r="BH180">
+      <c r="BH184">
         <v>11.5375</v>
       </c>
-      <c r="BI180">
+      <c r="BI184">
         <v>3.6</v>
       </c>
-      <c r="BJ180">
+      <c r="BJ184">
         <v>3.533831055297623</v>
       </c>
     </row>
